--- a/AMS_Standard_TestCases.xlsx
+++ b/AMS_Standard_TestCases.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="AMS_Project" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Summary" sheetId="1" r:id="rId4"/>
     <sheet state="visible" name="AMS_Master" sheetId="2" r:id="rId5"/>
     <sheet state="visible" name="AMS_Transaction" sheetId="3" r:id="rId6"/>
   </sheets>
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1759" uniqueCount="1070">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1819" uniqueCount="1110">
   <si>
     <t xml:space="preserve">Project Name / User Story Id: </t>
   </si>
@@ -114,7 +114,10 @@
     <t>Asset Retirement</t>
   </si>
   <si>
-    <t>Inprogress</t>
+    <t>Internal Asset Transfer</t>
+  </si>
+  <si>
+    <t>inprogress</t>
   </si>
   <si>
     <t>S.No</t>
@@ -7148,9 +7151,19 @@
     3. Export to PDF
     4. Export to Excel
     5. Grid Customization icon button
-    6. Edit record button
-    7. Delete button
-    8. Report button</t>
+    6. Delete button
+    7. Report button</t>
+  </si>
+  <si>
+    <t>1. User navigate to Asset Retirement index page
+2. Below field should available under Asset Retirement index page
+    1. Add button
+    2. Searchbar
+    3. Export to PDF
+    4. Export to Excel
+    5. Grid Customization icon button
+    6. Delete button
+    7. Report button</t>
   </si>
   <si>
     <t>1. User navigate to Asset Retirement index page
@@ -7168,7 +7181,7 @@
     <t>ARET002</t>
   </si>
   <si>
-    <t>Create and approve Asset Retirement through Excel import</t>
+    <t>Create and Approve Asset Retirement - Upload the Assets through Excel</t>
   </si>
   <si>
     <t>Asset Details record should in Active status</t>
@@ -7182,12 +7195,27 @@
       <t xml:space="preserve">1. Login User1 and navigate to Asset Retirement screen
 2. Click the Add icon button under Asset Retirement index page
 3. Download the Asset Retirement Excel format in Asset Retirement Create screen
-4. Fill the active Asset details Barcode and Save the Excel file
+4. Fill the active Assets Barcodes and Save the Excel file
 5. Click the Select Files button and upload the updated Excel sheet in Asset Retirement Create screen
 6. Verify Asset details are shows in Line item table in Create Asset Retirement screen
 7. Enter the Disposal Value, Disposal Remarks, Disposal Date and Disposal Type
 8. After enter the values click  the Save button under Create Asset Retirement screen
-9. Verify  Asset Retirement record created in  Asset Retirement grid table
+9. Verify Retirement record created successfully and Status as </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">WaitingForApproval </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">in  Asset Retirement grid table
 10. User1 navigate to Master - Asset screen
 11. Verify  Asset Retirement created Asset record status changed to </t>
     </r>
@@ -7463,7 +7491,7 @@
     <t>ARET003</t>
   </si>
   <si>
-    <t>Create and Reject the Asset Retirement through Excel import</t>
+    <t>Create and Reject Asset Retirement - Upload the Assets through Excel</t>
   </si>
   <si>
     <r>
@@ -7479,9 +7507,24 @@
 6. Verify Asset details are shows in Line item table in Create Asset Retirement screen
 7. Enter the Disposal Value, Disposal Remarks, Disposal Date and Disposal Type
 8. After enter the values click  the Save button under Create Asset Retirement screen
-9. Verify  Asset Retirement record created in  Asset Retirement grid table
+9. Verify  Asset Retirement record created successfully and Status as </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">WaitingForApproval </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">in  Asset Retirement grid table
 10. User1 navigate to Master - Asset screen
-11. Verify  Asset Retirement created Asset record status changed to </t>
+11. Verify Retirement created Asset record status changed to </t>
     </r>
     <r>
       <rPr>
@@ -7830,7 +7873,7 @@
     <t>ARET005</t>
   </si>
   <si>
-    <t>Create and Approve Asset Retirement through manual Asset selection</t>
+    <t>Create and Approve Asset Retirement -  Select Assets through Search Assets</t>
   </si>
   <si>
     <r>
@@ -7845,9 +7888,24 @@
 6. Verify selected Asset details are available in Line item table in Create Asset Retirement screen
 7. Enter the Disposal Value, Disposal Remarks, Disposal Date and Disposal Type
 8. After enter the values click  the Save button under Create Asset Retirement screen
-9. Verify  Asset Retirement record created in  Asset Retirement grid table
+9. Verify  Asset Retirement record created successfully and Status as </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">WaitingForApproval </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">in  Asset Retirement grid table
 10. User1 navigate to Master - Asset screen
-11. Verify  Asset Retirement created Asset record status changed to </t>
+11. Verify Retirement created Asset record status changed to </t>
     </r>
     <r>
       <rPr>
@@ -8029,6 +8087,9 @@
     <t>ARET006</t>
   </si>
   <si>
+    <t>Create and Reject Asset Retirement -  Select Assets through Search Assets</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <rFont val="Arial"/>
@@ -8042,9 +8103,24 @@
 6. Verify Asset details are available in Line item table in Create Asset Retirement screen
 7. Enter the Disposal Value, Disposal Remarks, Disposal Date and Disposal Type
 8. After enter the values click  the Save button under Create Asset Retirement screen
-9. Verify  Asset Retirement record created in  Asset Retirement grid table
+9. Verify  Asset Retirement record created successfully and Status as </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">WaitingForApproval  </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">in  Asset Retirement grid table
 10. User1 navigate to Master - Asset screen
-11. Verify  Asset Retirement created Asset record status changed to </t>
+11. Verify Retirement created Asset record status changed to </t>
     </r>
     <r>
       <rPr>
@@ -8248,6 +8324,644 @@
         <color theme="1"/>
       </rPr>
       <t>Rejected</t>
+    </r>
+  </si>
+  <si>
+    <t>ARET007</t>
+  </si>
+  <si>
+    <t>Delete the Asset Retirement record</t>
+  </si>
+  <si>
+    <t>Asset Retirement record status should WaitingForApproval or Rejected</t>
+  </si>
+  <si>
+    <t>1. Navigate to Transaction -- Asset Retirement
+2. Click the WaitingForApproval or Rejected record Delete button in Asset Retirement grid table
+3. Accept the Delete confirmation popup in Asset Retirement screen
+4. Verify Asset Retirement record deleted successfully in Asset Retirement grid table</t>
+  </si>
+  <si>
+    <t>If accept the Delete confimation popup, Asset Retirement record deleted successfully in grid table</t>
+  </si>
+  <si>
+    <t>ARET008</t>
+  </si>
+  <si>
+    <t>Try to Delete Approved Retirement record</t>
+  </si>
+  <si>
+    <t>Asset Retirement record should Approved</t>
+  </si>
+  <si>
+    <t>1. Navigate to Transaction -- Asset Retirement
+2. Click the Approved Asset Retirement record Delete button under grid table
+3. Accept the Delete confirmation popup in Asset Retirement screen
+4. Verify system not allow to delete Asset Retirement process completed record</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">If try to delete Asset Retirement approved record , system shows </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Record cant able to delete,Process Completed </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>Alert popup</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">If try to delete Asset Retirement approved record , system shows </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Record cant able to delete,Process Completed </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>Alert popup</t>
+    </r>
+  </si>
+  <si>
+    <t>ARET009</t>
+  </si>
+  <si>
+    <t>View the Asset Details in Reports</t>
+  </si>
+  <si>
+    <t>1. Navigate to Transaction -- Asset Retirement
+2. Create a one Asset Retirement in Create Asset Retirement screen
+3. Then Click the Report button under Asset Retirement index page grid table
+4. Verify Asset Retirement created Asset details availale in Reports</t>
+  </si>
+  <si>
+    <t>1. User able to create the Asset Retirement for selected Assets
+2. If click the Report button in grid table, system shows Retirement selected Asset Details in Reports page</t>
+  </si>
+  <si>
+    <t>ARET010</t>
+  </si>
+  <si>
+    <t>Find the Asset Retirement records in global searchbar</t>
+  </si>
+  <si>
+    <t>1. Navigate to Transaction -- Asset Retirement
+2. Enter the invalid values in searchbar under Asset Retirement screen
+3. Verify enter invalid values  Asset Retirement index page shows empty grid table
+4. Enter the valid values in searchbar under Asset Retirement screen
+5. Verify system shows seach related records in grid table under Asset Retirement index page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. If enter invalid values in searchbar, system shows no records in grid table
+2. If enter valid search values , system shows search related records in grid table </t>
+  </si>
+  <si>
+    <t>ARET011</t>
+  </si>
+  <si>
+    <t>Download the PDF report for Asset Retirement records</t>
+  </si>
+  <si>
+    <t>1. Navigate to Transaction -- Asset Retirement
+2.  Click the Export to PDF button under Asset Retirement index page
+3. Verify Asset Retirement report downloaded in PDF format</t>
+  </si>
+  <si>
+    <t>When click the Export to PDF button in Asset Retirement index page, system download the Asset Retirement report in PDF format</t>
+  </si>
+  <si>
+    <t>ARET012</t>
+  </si>
+  <si>
+    <t>Download the Excel report for Asset Retirement records</t>
+  </si>
+  <si>
+    <t>1. Navigate to Transaction -- Asset Retirement
+2.  Click the Export to Excel button under Asset Retirement index page
+3. Verify Asset Retirement report downloaded in Excel format</t>
+  </si>
+  <si>
+    <t>When click the Export to Excel button in Asset Retirement index page, system download the Asset Retirement report in Excel format</t>
+  </si>
+  <si>
+    <t>IAT001</t>
+  </si>
+  <si>
+    <t>Verify below fields are availble in Internal Asset Transfer index page</t>
+  </si>
+  <si>
+    <t>1. Navigate to Internal Asset Transfer under Transaction
+2. Verify below fields are available under Internal Asset Transfer index page
+    1. Add button
+    2. Global searchbar
+    3. Export to PDF
+    4. Export to Excel
+    5. Grid Customize button
+    6. View icon button
+    7. Delete button
+    8. Report button</t>
+  </si>
+  <si>
+    <t>1. Navigate to Internal Asset Transfer index page.
+2. Below fields are available under Internal Asset Transfer index page
+    1. Add button
+    2. Global searchbar
+    3. Export to PDF
+    4. Export to Excel
+    5. Grid Customize button
+    6. View icon button
+    7. Delete button
+    8. Report button</t>
+  </si>
+  <si>
+    <t>IAT002</t>
+  </si>
+  <si>
+    <t>Create and Approve Internal Asset Transfer - Upload the Assets through Excel</t>
+  </si>
+  <si>
+    <t>Assets record should in Active status</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">1. Login User1 and navigate to  Internal Asset Transfer screen
+2. Click the Add icon button under  Internal Asset Transfer index page
+3. Download the Transfer Asset Excel format in Asset Transfer Create screen
+4. Fill the active Assets Barcodes and Save the Excel file
+5. Then Click the Select Files button and upload the updated Excel sheet in  Asset Transfer Create screen
+6. Verify Asset details are shows in Line item table in Create Asset Transfer screen
+7. Select the To Location details from location dropdown in Asset Transfer Create screen
+8. Click  the Save button under Create Asset Transfer screen
+9. Verify  Asset Transfer record created and Status as </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">WaitingForApproval </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">in Internal Asset Transfer grid table
+10. Then User1 navigate to Master - Asset screen
+11. Verify  Asset Transfered Assets record status changed to </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">WaitingForApproval
+</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">12. Click Asset record Edit/View button and move to Transfer history tab. Verify Old Location and New Location available in grid table with Status of </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">WaitingForApproval
+</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">13. Verify Approval history shows Asset Transfer with status of </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">WaitingForApproval </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">and Get the Asset Transfer Transaction No
+1. Login User2 and navigate to Approval --  Internal Asset Transfer Approval screen
+2. Find the Transaction No and Click the Edit button under Internal Asset Transfer Approval screen
+3. Verify Added Asset Transfer details Old locaiton and New Location shows properly under line item table in Edit  Internal Asset Transfer Approval screen
+4. Click the Approve button in Edit  Internal Asset Transfer Approval screen
+5. Verify Asset Transfer Approval record approved successfully in Internal Asset Transfer Approval screen
+1. Login User1 and move to Transaction - Internal Asset Transfer
+2. Verify Created  Asset Transfer Transaction status changed to </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Approved
+</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">3. Move to Master -- Asset and verify Assets Transfer approved Assets record status changed to </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Active
+</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">4. Open the Transfered Assets record and move to Transaction History Tab and Verify status changed to </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Active</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">
+5. Approval History tab --- Internal Asset Transfer -- status changed to </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Active
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>1. User navigate to Internal Asset Transfer index page
+2. If click the Add button, system navigate to Create Internal Asset Transfer screen
+3. User able dowload excel and upload the excel in Create Asset Transfer screen
+4. Once upload the excel, Assets Details shows in Line Item table
+5. User should select the To Location in Asset Transfer create screen
+6. Click the Save button, system shows</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> Record Saved Successfully </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Alert popup
+7. Asset Transfer record created with </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>WaitingForApproval</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> status in  Internal Asset Transfer index page grid table
+8. Asset screen ---- Asset Transfer created Asset record status changed to </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">WaitingForApproval
+</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">9. Transaction History Tab - Transaction history available and Old location,New locaiton, Status as </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">WaitingForApproval
+</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">9. Approval history Tab - Shows Asset Transfer history status as </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>WaitingForApproval</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">
+1. User2 login and moved to Internal Asset Transfer Approval screen
+2. Click Transaction record Edit button, system navigate to Edit  Internal Asset Transfer Approval screen
+3. Asset Transfer details are available in Line Item table in Edit  Internal Asset Transfer Approval screen
+4. Click the Approve button, system shows record Saved successfully alert popup
+1.Login User1 and navigate to Transaction -  Internal Asset Transfer
+2. Once Asset Transfer approved - Asset Transfer Transaction status changed to </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Approved
+</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">3. In Asset screen -  Asset Transfer approved asset record status changed to </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Active
+</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">4. Open the Asset record and verify Location changed in Basic details tab
+5. Transaction History tab -- Status changed to </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Active </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">in grid table
+6. Approval History Tab - Internal Asset Transfer Status changed to </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Active</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>1. User navigate to Internal Asset Transfer index page
+2. If click the Add button, system navigate to Create Internal Asset Transfer screen
+3. User able dowload excel and upload the excel in Create Asset Transfer screen
+4. Once upload the excel, Assets Details shows in Line Item table
+5. User should select the To Location in Asset Transfer create screen
+6. Click the Save button, system shows</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> Record Saved Successfully </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Alert popup
+7. Asset Transfer record created with </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>WaitingForApproval</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> status in  Internal Asset Transfer index page grid table
+8. Asset screen ---- Asset Transfer created Asset record status changed to </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">WaitingForApproval
+</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">9. Transaction History Tab - Transaction history available and Old location,New locaiton, Status as </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">WaitingForApproval
+</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">9. Approval history Tab - Shows Asset Transfer history status as </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>WaitingForApproval</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">
+1. User2 login and moved to Internal Asset Transfer Approval screen
+2. Click Transaction record Edit button, system navigate to Edit  Internal Asset Transfer Approval screen
+3. Asset Transfer details are available in Line Item table in Edit  Internal Asset Transfer Approval screen
+4. Click the Approve button, system shows record Saved successfully alert popup
+1.Login User1 and navigate to Transaction -  Internal Asset Transfer
+2. Once Asset Transfer approved - Asset Transfer Transaction status changed to </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Approved
+</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">3. In Asset screen -  Asset Transfer approved asset record status changed to </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Active
+</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">4. Open the Asset record and verify Location changed in Basic details tab
+5. Transaction History tab -- Status changed to </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Active </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">in grid table
+6. Approval History Tab - Internal Asset Transfer Status changed to </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Active</t>
     </r>
   </si>
 </sst>
@@ -9144,18 +9858,22 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18"/>
+      <c r="A31" s="16"/>
       <c r="B31" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C31" s="14" t="s">
+      <c r="C31" s="14">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="18"/>
+      <c r="B32" s="14" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
+      <c r="C32" s="14" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3"/>
@@ -12086,7 +12804,7 @@
   <mergeCells count="3">
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A12:A29"/>
-    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A30:A32"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B5">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -12128,55 +12846,55 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F1" s="21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G1" s="22" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H1" s="22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I1" s="22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J1" s="22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K1" s="23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L1" s="23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M1" s="23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N1" s="23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O1" s="23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P1" s="23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q1" s="24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R1" s="25"/>
       <c r="S1" s="25"/>
@@ -12196,25 +12914,25 @@
         <v>12</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E2" s="28"/>
       <c r="F2" s="29"/>
       <c r="G2" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H2" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I2" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J2" s="31"/>
       <c r="K2" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L2" s="33"/>
       <c r="M2" s="33"/>
@@ -12240,25 +12958,25 @@
         <v>12</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E3" s="35"/>
       <c r="F3" s="29"/>
       <c r="G3" s="30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H3" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I3" s="30" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J3" s="31"/>
       <c r="K3" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L3" s="33"/>
       <c r="M3" s="33"/>
@@ -12275,25 +12993,25 @@
         <v>12</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E4" s="35"/>
       <c r="F4" s="37"/>
       <c r="G4" s="30" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H4" s="30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I4" s="30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J4" s="31"/>
       <c r="K4" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L4" s="38"/>
       <c r="M4" s="38"/>
@@ -12319,25 +13037,25 @@
         <v>12</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E5" s="35"/>
       <c r="F5" s="29"/>
       <c r="G5" s="30" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H5" s="30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I5" s="30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J5" s="31"/>
       <c r="K5" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L5" s="33"/>
       <c r="M5" s="33"/>
@@ -12354,25 +13072,25 @@
         <v>12</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E6" s="35"/>
       <c r="F6" s="29"/>
       <c r="G6" s="30" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H6" s="30" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I6" s="30" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J6" s="31"/>
       <c r="K6" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L6" s="33"/>
       <c r="M6" s="33"/>
@@ -12389,27 +13107,27 @@
         <v>12</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F7" s="29"/>
       <c r="G7" s="30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H7" s="30" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I7" s="30" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J7" s="30"/>
       <c r="K7" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L7" s="33"/>
       <c r="M7" s="33"/>
@@ -12426,27 +13144,27 @@
         <v>12</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F8" s="29"/>
       <c r="G8" s="30" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H8" s="30" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I8" s="30" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J8" s="31"/>
       <c r="K8" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L8" s="33"/>
       <c r="M8" s="33"/>
@@ -12463,27 +13181,27 @@
         <v>12</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F9" s="29"/>
       <c r="G9" s="30" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J9" s="31"/>
       <c r="K9" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L9" s="33"/>
       <c r="M9" s="33"/>
@@ -12500,27 +13218,27 @@
         <v>12</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F10" s="29"/>
       <c r="G10" s="30" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H10" s="30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I10" s="30" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J10" s="31"/>
       <c r="K10" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L10" s="33"/>
       <c r="M10" s="33"/>
@@ -12537,27 +13255,27 @@
         <v>12</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F11" s="29"/>
       <c r="G11" s="30" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H11" s="30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I11" s="30" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J11" s="31"/>
       <c r="K11" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L11" s="33"/>
       <c r="M11" s="33"/>
@@ -12574,27 +13292,27 @@
         <v>12</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F12" s="29"/>
       <c r="G12" s="30" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H12" s="30" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I12" s="30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J12" s="31"/>
       <c r="K12" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L12" s="33"/>
       <c r="M12" s="33"/>
@@ -12611,29 +13329,29 @@
         <v>12</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F13" s="29"/>
       <c r="G13" s="30" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H13" s="30" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I13" s="30" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J13" s="30" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K13" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L13" s="33"/>
       <c r="M13" s="33"/>
@@ -12650,27 +13368,27 @@
         <v>12</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E14" s="28" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F14" s="29"/>
       <c r="G14" s="30" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H14" s="30" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I14" s="30" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J14" s="31"/>
       <c r="K14" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L14" s="33"/>
       <c r="M14" s="33"/>
@@ -12687,27 +13405,27 @@
         <v>12</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E15" s="28" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F15" s="29"/>
       <c r="G15" s="30" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H15" s="30" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I15" s="30" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J15" s="31"/>
       <c r="K15" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L15" s="33"/>
       <c r="M15" s="33"/>
@@ -12724,25 +13442,25 @@
         <v>13</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E16" s="40"/>
       <c r="F16" s="31"/>
       <c r="G16" s="30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H16" s="30" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I16" s="30" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J16" s="31"/>
       <c r="K16" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L16" s="33"/>
       <c r="M16" s="33"/>
@@ -12759,25 +13477,25 @@
         <v>13</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E17" s="40"/>
       <c r="F17" s="31"/>
       <c r="G17" s="30" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H17" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I17" s="30" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J17" s="31"/>
       <c r="K17" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L17" s="33"/>
       <c r="M17" s="33"/>
@@ -12794,25 +13512,25 @@
         <v>13</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E18" s="40"/>
       <c r="F18" s="31"/>
       <c r="G18" s="30" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H18" s="30" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I18" s="30" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J18" s="31"/>
       <c r="K18" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L18" s="33"/>
       <c r="M18" s="33"/>
@@ -12829,25 +13547,25 @@
         <v>13</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E19" s="40"/>
       <c r="F19" s="31"/>
       <c r="G19" s="30" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H19" s="30" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I19" s="30" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J19" s="31"/>
       <c r="K19" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L19" s="33"/>
       <c r="M19" s="33"/>
@@ -12864,25 +13582,25 @@
         <v>13</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E20" s="40"/>
       <c r="F20" s="31"/>
       <c r="G20" s="30" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H20" s="30" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I20" s="30" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J20" s="31"/>
       <c r="K20" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L20" s="33"/>
       <c r="M20" s="33"/>
@@ -12899,27 +13617,27 @@
         <v>13</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D21" s="30" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F21" s="31"/>
       <c r="G21" s="30" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H21" s="30" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I21" s="30" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J21" s="31"/>
       <c r="K21" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L21" s="33"/>
       <c r="M21" s="33"/>
@@ -12936,27 +13654,27 @@
         <v>13</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D22" s="41" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E22" s="27" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F22" s="29"/>
       <c r="G22" s="42" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H22" s="43" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I22" s="41" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J22" s="31"/>
       <c r="K22" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L22" s="33"/>
       <c r="M22" s="33"/>
@@ -12973,27 +13691,27 @@
         <v>13</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D23" s="30" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F23" s="31"/>
       <c r="G23" s="42" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H23" s="42" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I23" s="42" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J23" s="31"/>
       <c r="K23" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L23" s="33"/>
       <c r="M23" s="33"/>
@@ -13010,27 +13728,27 @@
         <v>13</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D24" s="30" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E24" s="27" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F24" s="31"/>
       <c r="G24" s="44" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H24" s="42" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I24" s="42" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J24" s="31"/>
       <c r="K24" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L24" s="33"/>
       <c r="M24" s="33"/>
@@ -13047,27 +13765,27 @@
         <v>13</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F25" s="29"/>
       <c r="G25" s="30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H25" s="30" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I25" s="30" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J25" s="31"/>
       <c r="K25" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L25" s="33"/>
       <c r="M25" s="33"/>
@@ -13084,27 +13802,27 @@
         <v>14</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D26" s="27" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E26" s="35"/>
       <c r="F26" s="29"/>
       <c r="G26" s="44" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H26" s="44" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I26" s="42" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J26" s="30" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K26" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L26" s="33"/>
       <c r="M26" s="33"/>
@@ -13121,25 +13839,25 @@
         <v>14</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D27" s="27" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E27" s="35"/>
       <c r="F27" s="45"/>
       <c r="G27" s="44" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H27" s="44" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I27" s="44" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J27" s="31"/>
       <c r="K27" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L27" s="33"/>
       <c r="M27" s="33"/>
@@ -13156,25 +13874,25 @@
         <v>14</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D28" s="27" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E28" s="35"/>
       <c r="F28" s="41"/>
       <c r="G28" s="44" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H28" s="44" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I28" s="44" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J28" s="31"/>
       <c r="K28" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L28" s="33"/>
       <c r="M28" s="33"/>
@@ -13191,25 +13909,25 @@
         <v>14</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D29" s="27" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E29" s="35"/>
       <c r="F29" s="41"/>
       <c r="G29" s="44" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H29" s="44" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I29" s="44" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J29" s="31"/>
       <c r="K29" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L29" s="33"/>
       <c r="M29" s="33"/>
@@ -13226,27 +13944,27 @@
         <v>14</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D30" s="27" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E30" s="35"/>
       <c r="F30" s="41" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G30" s="44" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H30" s="44" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I30" s="44" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J30" s="31"/>
       <c r="K30" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L30" s="33"/>
       <c r="M30" s="33"/>
@@ -13263,29 +13981,29 @@
         <v>14</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D31" s="27" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E31" s="28" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F31" s="41" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G31" s="44" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H31" s="44" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I31" s="44" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J31" s="31"/>
       <c r="K31" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L31" s="33"/>
       <c r="M31" s="33"/>
@@ -13302,27 +14020,27 @@
         <v>14</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D32" s="27" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E32" s="28" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F32" s="29"/>
       <c r="G32" s="44" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H32" s="44" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I32" s="42" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J32" s="31"/>
       <c r="K32" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L32" s="33"/>
       <c r="M32" s="33"/>
@@ -13339,27 +14057,27 @@
         <v>14</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D33" s="27" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E33" s="28" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F33" s="29"/>
       <c r="G33" s="44" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H33" s="44" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I33" s="44" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J33" s="31"/>
       <c r="K33" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L33" s="33"/>
       <c r="M33" s="33"/>
@@ -13376,27 +14094,27 @@
         <v>14</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D34" s="27" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E34" s="28" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F34" s="29"/>
       <c r="G34" s="44" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H34" s="44" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I34" s="44" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J34" s="31"/>
       <c r="K34" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L34" s="33"/>
       <c r="M34" s="33"/>
@@ -13413,29 +14131,29 @@
         <v>14</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D35" s="27" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E35" s="28" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F35" s="29"/>
       <c r="G35" s="44" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H35" s="44" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I35" s="44" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J35" s="30" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K35" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L35" s="33"/>
       <c r="M35" s="33"/>
@@ -13452,25 +14170,25 @@
         <v>15</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D36" s="27" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E36" s="35"/>
       <c r="F36" s="29"/>
       <c r="G36" s="30" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H36" s="30" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I36" s="30" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J36" s="31"/>
       <c r="K36" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L36" s="33"/>
       <c r="M36" s="33"/>
@@ -13487,25 +14205,25 @@
         <v>15</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D37" s="27" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E37" s="35"/>
       <c r="F37" s="29"/>
       <c r="G37" s="30" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H37" s="30" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I37" s="30" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J37" s="31"/>
       <c r="K37" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L37" s="33"/>
       <c r="M37" s="33"/>
@@ -13522,25 +14240,25 @@
         <v>15</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D38" s="27" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E38" s="35"/>
       <c r="F38" s="29"/>
       <c r="G38" s="30" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H38" s="30" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I38" s="30" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J38" s="31"/>
       <c r="K38" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L38" s="33"/>
       <c r="M38" s="33"/>
@@ -13557,25 +14275,25 @@
         <v>15</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D39" s="27" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E39" s="35"/>
       <c r="F39" s="29"/>
       <c r="G39" s="30" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H39" s="30" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I39" s="30" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J39" s="31"/>
       <c r="K39" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L39" s="33"/>
       <c r="M39" s="33"/>
@@ -13592,25 +14310,25 @@
         <v>15</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D40" s="27" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E40" s="35"/>
       <c r="F40" s="29"/>
       <c r="G40" s="30" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H40" s="30" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I40" s="30" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J40" s="31"/>
       <c r="K40" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L40" s="33"/>
       <c r="M40" s="33"/>
@@ -13627,27 +14345,27 @@
         <v>15</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D41" s="27" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E41" s="28" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F41" s="29"/>
       <c r="G41" s="30" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H41" s="30" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I41" s="30" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J41" s="31"/>
       <c r="K41" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L41" s="33"/>
       <c r="M41" s="33"/>
@@ -13664,29 +14382,29 @@
         <v>15</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D42" s="27" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E42" s="28" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F42" s="29"/>
       <c r="G42" s="30" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H42" s="30" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I42" s="30" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J42" s="30" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K42" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L42" s="33"/>
       <c r="M42" s="33"/>
@@ -13703,27 +14421,27 @@
         <v>15</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D43" s="27" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E43" s="28" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F43" s="29"/>
       <c r="G43" s="30" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H43" s="30" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I43" s="30" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J43" s="31"/>
       <c r="K43" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L43" s="33"/>
       <c r="M43" s="33"/>
@@ -13740,27 +14458,27 @@
         <v>15</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D44" s="27" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E44" s="28" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F44" s="29"/>
       <c r="G44" s="30" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H44" s="30" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I44" s="30" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J44" s="31"/>
       <c r="K44" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L44" s="33"/>
       <c r="M44" s="33"/>
@@ -13777,27 +14495,27 @@
         <v>15</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D45" s="27" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E45" s="28" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F45" s="29"/>
       <c r="G45" s="30" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H45" s="30" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I45" s="30" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J45" s="31"/>
       <c r="K45" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L45" s="33"/>
       <c r="M45" s="33"/>
@@ -13814,29 +14532,29 @@
         <v>15</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D46" s="27" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E46" s="28" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F46" s="29"/>
       <c r="G46" s="30" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H46" s="30" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I46" s="30" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J46" s="30" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K46" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L46" s="33"/>
       <c r="M46" s="33"/>
@@ -13853,29 +14571,29 @@
         <v>15</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D47" s="27" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E47" s="28" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F47" s="29"/>
       <c r="G47" s="30" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H47" s="30" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I47" s="30" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J47" s="30" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K47" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L47" s="33"/>
       <c r="M47" s="33"/>
@@ -13892,27 +14610,27 @@
         <v>15</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D48" s="27" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E48" s="28" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F48" s="29"/>
       <c r="G48" s="30" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H48" s="30" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I48" s="30" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J48" s="31"/>
       <c r="K48" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L48" s="33"/>
       <c r="M48" s="33"/>
@@ -13929,27 +14647,27 @@
         <v>15</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D49" s="27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E49" s="28" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F49" s="29"/>
       <c r="G49" s="30" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H49" s="30" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I49" s="30" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J49" s="31"/>
       <c r="K49" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L49" s="33"/>
       <c r="M49" s="33"/>
@@ -13966,25 +14684,25 @@
         <v>16</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D50" s="27" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E50" s="35"/>
       <c r="F50" s="29"/>
       <c r="G50" s="30" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H50" s="30" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I50" s="30" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J50" s="31"/>
       <c r="K50" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L50" s="33"/>
       <c r="M50" s="33"/>
@@ -14001,25 +14719,25 @@
         <v>16</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D51" s="27" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E51" s="35"/>
       <c r="F51" s="29"/>
       <c r="G51" s="30" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H51" s="30" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I51" s="30" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J51" s="31"/>
       <c r="K51" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L51" s="33"/>
       <c r="M51" s="33"/>
@@ -14036,25 +14754,25 @@
         <v>16</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D52" s="27" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E52" s="35"/>
       <c r="F52" s="29"/>
       <c r="G52" s="30" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H52" s="30" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I52" s="30" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J52" s="31"/>
       <c r="K52" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L52" s="33"/>
       <c r="M52" s="33"/>
@@ -14071,25 +14789,25 @@
         <v>16</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D53" s="27" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E53" s="35"/>
       <c r="F53" s="29"/>
       <c r="G53" s="30" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H53" s="30" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="I53" s="30" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J53" s="31"/>
       <c r="K53" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L53" s="33"/>
       <c r="M53" s="33"/>
@@ -14106,25 +14824,25 @@
         <v>16</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D54" s="27" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E54" s="35"/>
       <c r="F54" s="29"/>
       <c r="G54" s="30" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H54" s="30" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I54" s="30" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J54" s="31"/>
       <c r="K54" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L54" s="33"/>
       <c r="M54" s="33"/>
@@ -14141,25 +14859,25 @@
         <v>16</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D55" s="27" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E55" s="35"/>
       <c r="F55" s="29"/>
       <c r="G55" s="30" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H55" s="30" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I55" s="30" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J55" s="31"/>
       <c r="K55" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L55" s="33"/>
       <c r="M55" s="33"/>
@@ -14176,27 +14894,27 @@
         <v>16</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D56" s="27" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E56" s="28" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F56" s="29"/>
       <c r="G56" s="30" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H56" s="30" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I56" s="30" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J56" s="31"/>
       <c r="K56" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L56" s="33"/>
       <c r="M56" s="33"/>
@@ -14213,27 +14931,27 @@
         <v>16</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D57" s="27" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E57" s="28" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F57" s="29"/>
       <c r="G57" s="30" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H57" s="30" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I57" s="30" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J57" s="31"/>
       <c r="K57" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L57" s="33"/>
       <c r="M57" s="33"/>
@@ -14250,27 +14968,27 @@
         <v>16</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D58" s="27" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E58" s="28" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F58" s="29"/>
       <c r="G58" s="30" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H58" s="30" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I58" s="30" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J58" s="31"/>
       <c r="K58" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L58" s="33"/>
       <c r="M58" s="33"/>
@@ -14287,27 +15005,27 @@
         <v>16</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D59" s="27" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E59" s="28" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F59" s="29"/>
       <c r="G59" s="30" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H59" s="30" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I59" s="30" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J59" s="31"/>
       <c r="K59" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L59" s="33"/>
       <c r="M59" s="33"/>
@@ -14324,29 +15042,29 @@
         <v>16</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D60" s="27" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E60" s="28" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F60" s="29"/>
       <c r="G60" s="30" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H60" s="30" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I60" s="30" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J60" s="30" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K60" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L60" s="33"/>
       <c r="M60" s="33"/>
@@ -14363,29 +15081,29 @@
         <v>16</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D61" s="27" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E61" s="28" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F61" s="29"/>
       <c r="G61" s="30" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H61" s="30" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I61" s="30" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J61" s="30" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K61" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L61" s="33"/>
       <c r="M61" s="33"/>
@@ -14402,27 +15120,27 @@
         <v>16</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D62" s="27" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E62" s="28" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F62" s="29"/>
       <c r="G62" s="30" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H62" s="30" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="I62" s="30" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J62" s="31"/>
       <c r="K62" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L62" s="33"/>
       <c r="M62" s="33"/>
@@ -14439,27 +15157,27 @@
         <v>16</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D63" s="27" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E63" s="28" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F63" s="29"/>
       <c r="G63" s="30" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H63" s="30" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I63" s="30" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J63" s="31"/>
       <c r="K63" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L63" s="33"/>
       <c r="M63" s="33"/>
@@ -14476,25 +15194,25 @@
         <v>17</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D64" s="27" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E64" s="35"/>
       <c r="F64" s="29"/>
       <c r="G64" s="30" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H64" s="30" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="I64" s="30" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J64" s="31"/>
       <c r="K64" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L64" s="33"/>
       <c r="M64" s="33"/>
@@ -14511,25 +15229,25 @@
         <v>17</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D65" s="27" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E65" s="35"/>
       <c r="F65" s="29"/>
       <c r="G65" s="30" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H65" s="30" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I65" s="30" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J65" s="31"/>
       <c r="K65" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L65" s="33"/>
       <c r="M65" s="33"/>
@@ -14546,25 +15264,25 @@
         <v>17</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D66" s="27" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E66" s="35"/>
       <c r="F66" s="29"/>
       <c r="G66" s="30" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H66" s="30" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I66" s="30" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J66" s="31"/>
       <c r="K66" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L66" s="33"/>
       <c r="M66" s="33"/>
@@ -14581,25 +15299,25 @@
         <v>17</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D67" s="27" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E67" s="35"/>
       <c r="F67" s="29"/>
       <c r="G67" s="30" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H67" s="30" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I67" s="30" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="J67" s="31"/>
       <c r="K67" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L67" s="33"/>
       <c r="M67" s="33"/>
@@ -14616,25 +15334,25 @@
         <v>17</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D68" s="27" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E68" s="35"/>
       <c r="F68" s="29"/>
       <c r="G68" s="30" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H68" s="30" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="I68" s="30" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J68" s="31"/>
       <c r="K68" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L68" s="33"/>
       <c r="M68" s="33"/>
@@ -14651,25 +15369,25 @@
         <v>17</v>
       </c>
       <c r="C69" s="14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D69" s="27" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E69" s="35"/>
       <c r="F69" s="29"/>
       <c r="G69" s="30" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H69" s="30" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="I69" s="30" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J69" s="31"/>
       <c r="K69" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L69" s="33"/>
       <c r="M69" s="33"/>
@@ -14686,25 +15404,25 @@
         <v>17</v>
       </c>
       <c r="C70" s="14" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D70" s="27" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E70" s="35"/>
       <c r="F70" s="29"/>
       <c r="G70" s="30" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H70" s="30" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="I70" s="30" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J70" s="31"/>
       <c r="K70" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L70" s="33"/>
       <c r="M70" s="33"/>
@@ -14721,25 +15439,25 @@
         <v>17</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D71" s="27" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E71" s="35"/>
       <c r="F71" s="29"/>
       <c r="G71" s="30" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H71" s="30" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I71" s="30" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J71" s="31"/>
       <c r="K71" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L71" s="33"/>
       <c r="M71" s="33"/>
@@ -14756,25 +15474,25 @@
         <v>17</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D72" s="27" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E72" s="35"/>
       <c r="F72" s="29"/>
       <c r="G72" s="30" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H72" s="30" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="I72" s="30" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J72" s="31"/>
       <c r="K72" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L72" s="33"/>
       <c r="M72" s="33"/>
@@ -14791,25 +15509,25 @@
         <v>17</v>
       </c>
       <c r="C73" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D73" s="27" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E73" s="35"/>
       <c r="F73" s="29"/>
       <c r="G73" s="30" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H73" s="30" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I73" s="30" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J73" s="31"/>
       <c r="K73" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L73" s="33"/>
       <c r="M73" s="33"/>
@@ -14826,27 +15544,27 @@
         <v>17</v>
       </c>
       <c r="C74" s="14" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D74" s="27" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E74" s="28" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F74" s="29"/>
       <c r="G74" s="30" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H74" s="30" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I74" s="30" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J74" s="31"/>
       <c r="K74" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L74" s="33"/>
       <c r="M74" s="33"/>
@@ -14863,27 +15581,27 @@
         <v>17</v>
       </c>
       <c r="C75" s="14" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D75" s="27" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E75" s="28"/>
       <c r="F75" s="29"/>
       <c r="G75" s="30" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H75" s="30" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="I75" s="30" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J75" s="30" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K75" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L75" s="33"/>
       <c r="M75" s="33"/>
@@ -14900,25 +15618,25 @@
         <v>17</v>
       </c>
       <c r="C76" s="14" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D76" s="27" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E76" s="28"/>
       <c r="F76" s="29"/>
       <c r="G76" s="30" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H76" s="30" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="I76" s="30" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J76" s="31"/>
       <c r="K76" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L76" s="33"/>
       <c r="M76" s="33"/>
@@ -14935,25 +15653,25 @@
         <v>18</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D77" s="27" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E77" s="35"/>
       <c r="F77" s="29"/>
       <c r="G77" s="30" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H77" s="30" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="I77" s="30" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J77" s="31"/>
       <c r="K77" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L77" s="33"/>
       <c r="M77" s="33"/>
@@ -14970,25 +15688,25 @@
         <v>18</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D78" s="27" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E78" s="35"/>
       <c r="F78" s="29"/>
       <c r="G78" s="30" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H78" s="30" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="I78" s="30" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="J78" s="31"/>
       <c r="K78" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L78" s="33"/>
       <c r="M78" s="33"/>
@@ -15005,27 +15723,27 @@
         <v>18</v>
       </c>
       <c r="C79" s="14" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D79" s="27" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E79" s="28" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F79" s="29"/>
       <c r="G79" s="30" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H79" s="30" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I79" s="30" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="J79" s="31"/>
       <c r="K79" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L79" s="33"/>
       <c r="M79" s="33"/>
@@ -15042,27 +15760,27 @@
         <v>18</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D80" s="27" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E80" s="28" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F80" s="29"/>
       <c r="G80" s="30" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H80" s="30" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="I80" s="30" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J80" s="31"/>
       <c r="K80" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L80" s="33"/>
       <c r="M80" s="33"/>
@@ -15079,25 +15797,25 @@
         <v>18</v>
       </c>
       <c r="C81" s="14" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D81" s="27" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E81" s="35"/>
       <c r="F81" s="29"/>
       <c r="G81" s="30" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H81" s="30" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I81" s="30" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="J81" s="31"/>
       <c r="K81" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L81" s="33"/>
       <c r="M81" s="33"/>
@@ -15114,25 +15832,25 @@
         <v>18</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D82" s="27" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E82" s="35"/>
       <c r="F82" s="29"/>
       <c r="G82" s="30" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H82" s="30" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="I82" s="30" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="J82" s="31"/>
       <c r="K82" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L82" s="33"/>
       <c r="M82" s="33"/>
@@ -15149,25 +15867,25 @@
         <v>18</v>
       </c>
       <c r="C83" s="14" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D83" s="27" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E83" s="35"/>
       <c r="F83" s="29"/>
       <c r="G83" s="30" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H83" s="30" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="I83" s="30" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J83" s="31"/>
       <c r="K83" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L83" s="33"/>
       <c r="M83" s="33"/>
@@ -15184,25 +15902,25 @@
         <v>18</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D84" s="27" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E84" s="35"/>
       <c r="F84" s="29"/>
       <c r="G84" s="30" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H84" s="30" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="I84" s="30" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="J84" s="31"/>
       <c r="K84" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L84" s="33"/>
       <c r="M84" s="33"/>
@@ -15219,25 +15937,25 @@
         <v>18</v>
       </c>
       <c r="C85" s="14" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D85" s="27" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E85" s="35"/>
       <c r="F85" s="29"/>
       <c r="G85" s="30" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H85" s="30" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="I85" s="30" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="J85" s="31"/>
       <c r="K85" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L85" s="33"/>
       <c r="M85" s="33"/>
@@ -15254,25 +15972,25 @@
         <v>18</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D86" s="27" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E86" s="35"/>
       <c r="F86" s="29"/>
       <c r="G86" s="30" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H86" s="30" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="I86" s="30" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J86" s="31"/>
       <c r="K86" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L86" s="33"/>
       <c r="M86" s="33"/>
@@ -15289,27 +16007,27 @@
         <v>18</v>
       </c>
       <c r="C87" s="14" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D87" s="27" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E87" s="35"/>
       <c r="F87" s="29"/>
       <c r="G87" s="30" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H87" s="30" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="I87" s="30" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J87" s="30" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K87" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L87" s="33"/>
       <c r="M87" s="33"/>
@@ -15326,25 +16044,25 @@
         <v>18</v>
       </c>
       <c r="C88" s="14" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D88" s="27" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E88" s="35"/>
       <c r="F88" s="29"/>
       <c r="G88" s="30" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H88" s="30" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="I88" s="30" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="J88" s="31"/>
       <c r="K88" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L88" s="33"/>
       <c r="M88" s="33"/>
@@ -15361,25 +16079,25 @@
         <v>19</v>
       </c>
       <c r="C89" s="14" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D89" s="27" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E89" s="35"/>
       <c r="F89" s="29"/>
       <c r="G89" s="30" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H89" s="30" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="I89" s="30" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="J89" s="31"/>
       <c r="K89" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L89" s="33"/>
       <c r="M89" s="33"/>
@@ -15396,25 +16114,25 @@
         <v>19</v>
       </c>
       <c r="C90" s="14" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D90" s="27" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E90" s="35"/>
       <c r="F90" s="29"/>
       <c r="G90" s="30" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H90" s="30" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="I90" s="30" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="J90" s="31"/>
       <c r="K90" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L90" s="33"/>
       <c r="M90" s="33"/>
@@ -15431,29 +16149,29 @@
         <v>19</v>
       </c>
       <c r="C91" s="14" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D91" s="27" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E91" s="28" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F91" s="41" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="G91" s="30" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H91" s="30" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="I91" s="30" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="J91" s="31"/>
       <c r="K91" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L91" s="33"/>
       <c r="M91" s="33"/>
@@ -15470,25 +16188,25 @@
         <v>19</v>
       </c>
       <c r="C92" s="14" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D92" s="27" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E92" s="35"/>
       <c r="F92" s="29"/>
       <c r="G92" s="30" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H92" s="30" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I92" s="30" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="J92" s="31"/>
       <c r="K92" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L92" s="33"/>
       <c r="M92" s="33"/>
@@ -15505,25 +16223,25 @@
         <v>19</v>
       </c>
       <c r="C93" s="14" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D93" s="27" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E93" s="35"/>
       <c r="F93" s="29"/>
       <c r="G93" s="30" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H93" s="30" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="I93" s="30" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="J93" s="31"/>
       <c r="K93" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L93" s="33"/>
       <c r="M93" s="33"/>
@@ -15540,25 +16258,25 @@
         <v>19</v>
       </c>
       <c r="C94" s="14" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D94" s="27" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E94" s="35"/>
       <c r="F94" s="29"/>
       <c r="G94" s="30" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H94" s="30" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I94" s="30" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J94" s="31"/>
       <c r="K94" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L94" s="33"/>
       <c r="M94" s="33"/>
@@ -15575,25 +16293,25 @@
         <v>19</v>
       </c>
       <c r="C95" s="14" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D95" s="27" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E95" s="35"/>
       <c r="F95" s="29"/>
       <c r="G95" s="30" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H95" s="30" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="I95" s="30" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J95" s="31"/>
       <c r="K95" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L95" s="33"/>
       <c r="M95" s="33"/>
@@ -15610,25 +16328,25 @@
         <v>19</v>
       </c>
       <c r="C96" s="14" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D96" s="27" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E96" s="35"/>
       <c r="F96" s="29"/>
       <c r="G96" s="30" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H96" s="30" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="I96" s="30" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="J96" s="31"/>
       <c r="K96" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L96" s="33"/>
       <c r="M96" s="33"/>
@@ -15645,25 +16363,25 @@
         <v>19</v>
       </c>
       <c r="C97" s="14" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D97" s="27" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E97" s="35"/>
       <c r="F97" s="29"/>
       <c r="G97" s="30" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H97" s="30" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I97" s="30" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="J97" s="31"/>
       <c r="K97" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L97" s="33"/>
       <c r="M97" s="33"/>
@@ -15680,25 +16398,25 @@
         <v>19</v>
       </c>
       <c r="C98" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D98" s="27" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E98" s="35"/>
       <c r="F98" s="29"/>
       <c r="G98" s="30" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H98" s="30" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="I98" s="30" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="J98" s="31"/>
       <c r="K98" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L98" s="33"/>
       <c r="M98" s="33"/>
@@ -15715,27 +16433,27 @@
         <v>19</v>
       </c>
       <c r="C99" s="14" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D99" s="27" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E99" s="35"/>
       <c r="F99" s="29"/>
       <c r="G99" s="30" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H99" s="30" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="I99" s="30" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="J99" s="30" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="K99" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L99" s="33"/>
       <c r="M99" s="33"/>
@@ -15752,25 +16470,25 @@
         <v>19</v>
       </c>
       <c r="C100" s="14" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D100" s="27" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E100" s="35"/>
       <c r="F100" s="29"/>
       <c r="G100" s="30" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H100" s="30" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="I100" s="30" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="J100" s="31"/>
       <c r="K100" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L100" s="33"/>
       <c r="M100" s="33"/>
@@ -15787,27 +16505,27 @@
         <v>20</v>
       </c>
       <c r="C101" s="14" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D101" s="27" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E101" s="35"/>
       <c r="F101" s="29"/>
       <c r="G101" s="30" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H101" s="30" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="I101" s="30" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="J101" s="30" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K101" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L101" s="33"/>
       <c r="M101" s="33"/>
@@ -15824,25 +16542,25 @@
         <v>20</v>
       </c>
       <c r="C102" s="14" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D102" s="27" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E102" s="35"/>
       <c r="F102" s="29"/>
       <c r="G102" s="30" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H102" s="30" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="I102" s="30" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="J102" s="31"/>
       <c r="K102" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L102" s="33"/>
       <c r="M102" s="33"/>
@@ -15859,25 +16577,25 @@
         <v>20</v>
       </c>
       <c r="C103" s="14" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D103" s="27" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E103" s="35"/>
       <c r="F103" s="29"/>
       <c r="G103" s="30" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H103" s="30" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="I103" s="30" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="J103" s="31"/>
       <c r="K103" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L103" s="33"/>
       <c r="M103" s="33"/>
@@ -15894,25 +16612,25 @@
         <v>20</v>
       </c>
       <c r="C104" s="14" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D104" s="27" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E104" s="35"/>
       <c r="F104" s="29"/>
       <c r="G104" s="30" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H104" s="30" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="I104" s="30" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="J104" s="31"/>
       <c r="K104" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L104" s="33"/>
       <c r="M104" s="33"/>
@@ -15929,25 +16647,25 @@
         <v>20</v>
       </c>
       <c r="C105" s="14" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D105" s="27" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E105" s="35"/>
       <c r="F105" s="29"/>
       <c r="G105" s="30" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H105" s="30" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I105" s="30" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J105" s="31"/>
       <c r="K105" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L105" s="33"/>
       <c r="M105" s="33"/>
@@ -15964,25 +16682,25 @@
         <v>20</v>
       </c>
       <c r="C106" s="14" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D106" s="27" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E106" s="35"/>
       <c r="F106" s="29"/>
       <c r="G106" s="30" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H106" s="30" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="I106" s="30" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="J106" s="31"/>
       <c r="K106" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L106" s="33"/>
       <c r="M106" s="33"/>
@@ -15999,25 +16717,25 @@
         <v>20</v>
       </c>
       <c r="C107" s="14" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D107" s="27" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E107" s="35"/>
       <c r="F107" s="29"/>
       <c r="G107" s="30" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H107" s="30" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="I107" s="30" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="J107" s="31"/>
       <c r="K107" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L107" s="33"/>
       <c r="M107" s="33"/>
@@ -16034,25 +16752,25 @@
         <v>20</v>
       </c>
       <c r="C108" s="14" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D108" s="27" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E108" s="35"/>
       <c r="F108" s="29"/>
       <c r="G108" s="30" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H108" s="30" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="I108" s="30" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="J108" s="31"/>
       <c r="K108" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L108" s="33"/>
       <c r="M108" s="33"/>
@@ -16069,25 +16787,25 @@
         <v>20</v>
       </c>
       <c r="C109" s="14" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D109" s="27" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E109" s="35"/>
       <c r="F109" s="29"/>
       <c r="G109" s="30" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H109" s="30" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="I109" s="30" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="J109" s="31"/>
       <c r="K109" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L109" s="33"/>
       <c r="M109" s="33"/>
@@ -16104,25 +16822,25 @@
         <v>20</v>
       </c>
       <c r="C110" s="14" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D110" s="27" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E110" s="35"/>
       <c r="F110" s="29"/>
       <c r="G110" s="30" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H110" s="30" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="I110" s="30" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="J110" s="31"/>
       <c r="K110" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L110" s="33"/>
       <c r="M110" s="33"/>
@@ -16139,27 +16857,27 @@
         <v>20</v>
       </c>
       <c r="C111" s="14" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D111" s="27" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E111" s="35"/>
       <c r="F111" s="29"/>
       <c r="G111" s="30" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H111" s="30" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="I111" s="30" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="J111" s="30" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K111" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L111" s="33"/>
       <c r="M111" s="33"/>
@@ -16176,25 +16894,25 @@
         <v>20</v>
       </c>
       <c r="C112" s="14" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D112" s="27" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E112" s="35"/>
       <c r="F112" s="29"/>
       <c r="G112" s="30" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H112" s="30" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="I112" s="30" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="J112" s="31"/>
       <c r="K112" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L112" s="33"/>
       <c r="M112" s="33"/>
@@ -16211,25 +16929,25 @@
         <v>21</v>
       </c>
       <c r="C113" s="14" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D113" s="27" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E113" s="35"/>
       <c r="F113" s="29"/>
       <c r="G113" s="30" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H113" s="30" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="I113" s="30" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="J113" s="31"/>
       <c r="K113" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L113" s="33"/>
       <c r="M113" s="33"/>
@@ -16246,25 +16964,25 @@
         <v>21</v>
       </c>
       <c r="C114" s="14" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D114" s="27" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E114" s="35"/>
       <c r="F114" s="29"/>
       <c r="G114" s="30" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H114" s="30" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="I114" s="30" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="J114" s="31"/>
       <c r="K114" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L114" s="33"/>
       <c r="M114" s="33"/>
@@ -16281,25 +16999,25 @@
         <v>21</v>
       </c>
       <c r="C115" s="14" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D115" s="27" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E115" s="35"/>
       <c r="F115" s="29"/>
       <c r="G115" s="30" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H115" s="30" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="I115" s="30" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J115" s="31"/>
       <c r="K115" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L115" s="33"/>
       <c r="M115" s="33"/>
@@ -16316,25 +17034,25 @@
         <v>21</v>
       </c>
       <c r="C116" s="14" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D116" s="27" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E116" s="35"/>
       <c r="F116" s="29"/>
       <c r="G116" s="30" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H116" s="30" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="I116" s="30" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="J116" s="31"/>
       <c r="K116" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L116" s="33"/>
       <c r="M116" s="33"/>
@@ -16351,25 +17069,25 @@
         <v>21</v>
       </c>
       <c r="C117" s="14" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D117" s="27" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E117" s="35"/>
       <c r="F117" s="29"/>
       <c r="G117" s="30" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H117" s="30" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="I117" s="30" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="J117" s="31"/>
       <c r="K117" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L117" s="33"/>
       <c r="M117" s="33"/>
@@ -16386,25 +17104,25 @@
         <v>21</v>
       </c>
       <c r="C118" s="14" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D118" s="27" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E118" s="35"/>
       <c r="F118" s="29"/>
       <c r="G118" s="30" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H118" s="30" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="I118" s="30" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="J118" s="31"/>
       <c r="K118" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L118" s="33"/>
       <c r="M118" s="33"/>
@@ -16421,25 +17139,25 @@
         <v>21</v>
       </c>
       <c r="C119" s="14" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D119" s="27" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E119" s="35"/>
       <c r="F119" s="29"/>
       <c r="G119" s="30" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H119" s="30" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="I119" s="30" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="J119" s="31"/>
       <c r="K119" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L119" s="33"/>
       <c r="M119" s="33"/>
@@ -16456,25 +17174,25 @@
         <v>21</v>
       </c>
       <c r="C120" s="14" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D120" s="27" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E120" s="35"/>
       <c r="F120" s="29"/>
       <c r="G120" s="30" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H120" s="30" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="I120" s="30" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="J120" s="31"/>
       <c r="K120" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L120" s="33"/>
       <c r="M120" s="33"/>
@@ -16491,25 +17209,25 @@
         <v>21</v>
       </c>
       <c r="C121" s="14" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D121" s="27" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E121" s="35"/>
       <c r="F121" s="29"/>
       <c r="G121" s="30" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H121" s="30" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="I121" s="30" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="J121" s="31"/>
       <c r="K121" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L121" s="33"/>
       <c r="M121" s="33"/>
@@ -16526,25 +17244,25 @@
         <v>21</v>
       </c>
       <c r="C122" s="14" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D122" s="27" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E122" s="35"/>
       <c r="F122" s="29"/>
       <c r="G122" s="30" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H122" s="30" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="I122" s="30" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="J122" s="31"/>
       <c r="K122" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L122" s="33"/>
       <c r="M122" s="33"/>
@@ -16561,27 +17279,27 @@
         <v>21</v>
       </c>
       <c r="C123" s="14" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D123" s="27" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E123" s="35"/>
       <c r="F123" s="29"/>
       <c r="G123" s="30" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H123" s="30" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="I123" s="30" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="J123" s="30" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K123" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L123" s="33"/>
       <c r="M123" s="33"/>
@@ -16598,25 +17316,25 @@
         <v>21</v>
       </c>
       <c r="C124" s="14" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D124" s="27" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E124" s="35"/>
       <c r="F124" s="29"/>
       <c r="G124" s="30" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H124" s="30" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="I124" s="30" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="J124" s="31"/>
       <c r="K124" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L124" s="33"/>
       <c r="M124" s="33"/>
@@ -16633,27 +17351,27 @@
         <v>22</v>
       </c>
       <c r="C125" s="14" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D125" s="27" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E125" s="28" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F125" s="29"/>
       <c r="G125" s="30" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H125" s="30" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="I125" s="30" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="J125" s="31"/>
       <c r="K125" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L125" s="33"/>
       <c r="M125" s="33"/>
@@ -16670,27 +17388,27 @@
         <v>22</v>
       </c>
       <c r="C126" s="14" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D126" s="27" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E126" s="28" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F126" s="29"/>
       <c r="G126" s="30" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H126" s="30" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="I126" s="30" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="J126" s="31"/>
       <c r="K126" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L126" s="33"/>
       <c r="M126" s="33"/>
@@ -16707,27 +17425,27 @@
         <v>22</v>
       </c>
       <c r="C127" s="14" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D127" s="27" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E127" s="28" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F127" s="29"/>
       <c r="G127" s="30" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H127" s="30" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="I127" s="30" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="J127" s="31"/>
       <c r="K127" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L127" s="33"/>
       <c r="M127" s="33"/>
@@ -16744,25 +17462,25 @@
         <v>22</v>
       </c>
       <c r="C128" s="14" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D128" s="27" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E128" s="35"/>
       <c r="F128" s="29"/>
       <c r="G128" s="30" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H128" s="30" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="I128" s="30" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="J128" s="31"/>
       <c r="K128" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L128" s="33"/>
       <c r="M128" s="33"/>
@@ -16779,25 +17497,25 @@
         <v>22</v>
       </c>
       <c r="C129" s="14" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D129" s="27" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E129" s="35"/>
       <c r="F129" s="29"/>
       <c r="G129" s="30" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H129" s="30" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="I129" s="30" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="J129" s="31"/>
       <c r="K129" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L129" s="33"/>
       <c r="M129" s="33"/>
@@ -16814,25 +17532,25 @@
         <v>22</v>
       </c>
       <c r="C130" s="14" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D130" s="27" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E130" s="35"/>
       <c r="F130" s="29"/>
       <c r="G130" s="30" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H130" s="30" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="I130" s="30" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="J130" s="31"/>
       <c r="K130" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L130" s="33"/>
       <c r="M130" s="33"/>
@@ -16849,25 +17567,25 @@
         <v>22</v>
       </c>
       <c r="C131" s="14" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D131" s="27" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E131" s="35"/>
       <c r="F131" s="29"/>
       <c r="G131" s="30" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H131" s="30" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="I131" s="30" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="J131" s="31"/>
       <c r="K131" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L131" s="33"/>
       <c r="M131" s="33"/>
@@ -16884,25 +17602,25 @@
         <v>22</v>
       </c>
       <c r="C132" s="14" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D132" s="27" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E132" s="35"/>
       <c r="F132" s="29"/>
       <c r="G132" s="30" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H132" s="30" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="I132" s="30" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="J132" s="31"/>
       <c r="K132" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L132" s="33"/>
       <c r="M132" s="33"/>
@@ -16919,25 +17637,25 @@
         <v>22</v>
       </c>
       <c r="C133" s="14" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D133" s="27" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="E133" s="35"/>
       <c r="F133" s="29"/>
       <c r="G133" s="30" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H133" s="30" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="I133" s="30" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="J133" s="31"/>
       <c r="K133" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L133" s="33"/>
       <c r="M133" s="33"/>
@@ -16954,25 +17672,25 @@
         <v>22</v>
       </c>
       <c r="C134" s="14" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D134" s="27" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="E134" s="35"/>
       <c r="F134" s="29"/>
       <c r="G134" s="30" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H134" s="30" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="I134" s="30" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="J134" s="31"/>
       <c r="K134" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L134" s="33"/>
       <c r="M134" s="33"/>
@@ -16989,27 +17707,27 @@
         <v>22</v>
       </c>
       <c r="C135" s="14" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D135" s="27" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E135" s="35"/>
       <c r="F135" s="29"/>
       <c r="G135" s="30" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H135" s="30" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I135" s="30" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="J135" s="30" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K135" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L135" s="33"/>
       <c r="M135" s="33"/>
@@ -17026,25 +17744,25 @@
         <v>22</v>
       </c>
       <c r="C136" s="14" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D136" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E136" s="35"/>
       <c r="F136" s="29"/>
       <c r="G136" s="30" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H136" s="30" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="I136" s="30" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="J136" s="31"/>
       <c r="K136" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L136" s="33"/>
       <c r="M136" s="33"/>
@@ -17061,27 +17779,27 @@
         <v>23</v>
       </c>
       <c r="C137" s="14" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D137" s="27" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E137" s="28" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F137" s="29"/>
       <c r="G137" s="30" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H137" s="30" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="I137" s="30" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="J137" s="31"/>
       <c r="K137" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L137" s="33"/>
       <c r="M137" s="33"/>
@@ -17098,25 +17816,25 @@
         <v>23</v>
       </c>
       <c r="C138" s="14" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D138" s="27" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E138" s="35"/>
       <c r="F138" s="29"/>
       <c r="G138" s="30" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H138" s="30" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="I138" s="30" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="J138" s="31"/>
       <c r="K138" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L138" s="33"/>
       <c r="M138" s="33"/>
@@ -17133,25 +17851,25 @@
         <v>23</v>
       </c>
       <c r="C139" s="14" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D139" s="27" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E139" s="28"/>
       <c r="F139" s="29"/>
       <c r="G139" s="30" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H139" s="30" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="I139" s="30" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="J139" s="31"/>
       <c r="K139" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L139" s="33"/>
       <c r="M139" s="33"/>
@@ -17168,25 +17886,25 @@
         <v>23</v>
       </c>
       <c r="C140" s="14" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D140" s="27" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="E140" s="35"/>
       <c r="F140" s="29"/>
       <c r="G140" s="30" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H140" s="30" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="I140" s="30" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="J140" s="31"/>
       <c r="K140" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L140" s="33"/>
       <c r="M140" s="33"/>
@@ -17203,25 +17921,25 @@
         <v>23</v>
       </c>
       <c r="C141" s="14" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D141" s="27" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E141" s="35"/>
       <c r="F141" s="29"/>
       <c r="G141" s="30" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H141" s="30" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="I141" s="30" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="J141" s="31"/>
       <c r="K141" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L141" s="33"/>
       <c r="M141" s="33"/>
@@ -17238,25 +17956,25 @@
         <v>23</v>
       </c>
       <c r="C142" s="14" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D142" s="27" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E142" s="35"/>
       <c r="F142" s="29"/>
       <c r="G142" s="30" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H142" s="30" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="I142" s="30" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="J142" s="31"/>
       <c r="K142" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L142" s="33"/>
       <c r="M142" s="33"/>
@@ -17273,25 +17991,25 @@
         <v>23</v>
       </c>
       <c r="C143" s="14" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D143" s="27" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E143" s="35"/>
       <c r="F143" s="29"/>
       <c r="G143" s="30" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H143" s="30" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="I143" s="30" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="J143" s="31"/>
       <c r="K143" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L143" s="33"/>
       <c r="M143" s="33"/>
@@ -17308,25 +18026,25 @@
         <v>23</v>
       </c>
       <c r="C144" s="14" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D144" s="27" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E144" s="35"/>
       <c r="F144" s="29"/>
       <c r="G144" s="30" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H144" s="30" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="I144" s="30" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="J144" s="31"/>
       <c r="K144" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L144" s="33"/>
       <c r="M144" s="33"/>
@@ -17343,25 +18061,25 @@
         <v>23</v>
       </c>
       <c r="C145" s="14" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D145" s="27" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E145" s="35"/>
       <c r="F145" s="29"/>
       <c r="G145" s="30" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H145" s="30" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="I145" s="30" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="J145" s="31"/>
       <c r="K145" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L145" s="33"/>
       <c r="M145" s="33"/>
@@ -17378,27 +18096,27 @@
         <v>23</v>
       </c>
       <c r="C146" s="14" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D146" s="27" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E146" s="35"/>
       <c r="F146" s="29"/>
       <c r="G146" s="30" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H146" s="30" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="I146" s="30" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="J146" s="30" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K146" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L146" s="33"/>
       <c r="M146" s="33"/>
@@ -17415,25 +18133,25 @@
         <v>23</v>
       </c>
       <c r="C147" s="14" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D147" s="27" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E147" s="35"/>
       <c r="F147" s="29"/>
       <c r="G147" s="30" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H147" s="30" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="I147" s="30" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="J147" s="31"/>
       <c r="K147" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L147" s="33"/>
       <c r="M147" s="33"/>
@@ -17450,25 +18168,25 @@
         <v>24</v>
       </c>
       <c r="C148" s="14" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D148" s="27" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E148" s="35"/>
       <c r="F148" s="29"/>
       <c r="G148" s="30" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H148" s="30" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="I148" s="30" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="J148" s="31"/>
       <c r="K148" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L148" s="33"/>
       <c r="M148" s="33"/>
@@ -17485,27 +18203,27 @@
         <v>24</v>
       </c>
       <c r="C149" s="14" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D149" s="27" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="E149" s="35"/>
       <c r="F149" s="41" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="G149" s="30" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H149" s="30" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="I149" s="30" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="J149" s="31"/>
       <c r="K149" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L149" s="33"/>
       <c r="M149" s="33"/>
@@ -17522,25 +18240,25 @@
         <v>24</v>
       </c>
       <c r="C150" s="14" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D150" s="27" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="E150" s="35"/>
       <c r="F150" s="29"/>
       <c r="G150" s="30" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H150" s="30" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="I150" s="30" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="J150" s="31"/>
       <c r="K150" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L150" s="33"/>
       <c r="M150" s="33"/>
@@ -17557,25 +18275,25 @@
         <v>24</v>
       </c>
       <c r="C151" s="14" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D151" s="27" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="E151" s="35"/>
       <c r="F151" s="29"/>
       <c r="G151" s="30" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H151" s="30" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="I151" s="30" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="J151" s="31"/>
       <c r="K151" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L151" s="33"/>
       <c r="M151" s="33"/>
@@ -17592,25 +18310,25 @@
         <v>24</v>
       </c>
       <c r="C152" s="14" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D152" s="27" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="E152" s="35"/>
       <c r="F152" s="29"/>
       <c r="G152" s="30" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H152" s="30" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="I152" s="30" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="J152" s="31"/>
       <c r="K152" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L152" s="33"/>
       <c r="M152" s="33"/>
@@ -17627,25 +18345,25 @@
         <v>24</v>
       </c>
       <c r="C153" s="14" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D153" s="27" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="E153" s="35"/>
       <c r="F153" s="29"/>
       <c r="G153" s="30" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H153" s="30" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="I153" s="30" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="J153" s="31"/>
       <c r="K153" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L153" s="33"/>
       <c r="M153" s="33"/>
@@ -17662,27 +18380,27 @@
         <v>24</v>
       </c>
       <c r="C154" s="14" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D154" s="27" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="E154" s="35"/>
       <c r="F154" s="29"/>
       <c r="G154" s="30" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H154" s="30" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="I154" s="30" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="J154" s="30" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="K154" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L154" s="33"/>
       <c r="M154" s="33"/>
@@ -17699,27 +18417,27 @@
         <v>24</v>
       </c>
       <c r="C155" s="14" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D155" s="27" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E155" s="35"/>
       <c r="F155" s="29"/>
       <c r="G155" s="30" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H155" s="30" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="I155" s="30" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="J155" s="30" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="K155" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L155" s="33"/>
       <c r="M155" s="33"/>
@@ -17736,27 +18454,27 @@
         <v>24</v>
       </c>
       <c r="C156" s="14" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="D156" s="27" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="E156" s="35"/>
       <c r="F156" s="29"/>
       <c r="G156" s="30" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H156" s="30" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="I156" s="30" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="J156" s="30" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="K156" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L156" s="33"/>
       <c r="M156" s="33"/>
@@ -17770,28 +18488,28 @@
         <v>156.0</v>
       </c>
       <c r="B157" s="14" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C157" s="14" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D157" s="27" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="E157" s="35"/>
       <c r="F157" s="29"/>
       <c r="G157" s="30" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H157" s="30" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="I157" s="30" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="J157" s="31"/>
       <c r="K157" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L157" s="33"/>
       <c r="M157" s="33"/>
@@ -17805,28 +18523,28 @@
         <v>157.0</v>
       </c>
       <c r="B158" s="14" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C158" s="14" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="D158" s="27" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="E158" s="35"/>
       <c r="F158" s="29"/>
       <c r="G158" s="30" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H158" s="30" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="I158" s="30" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="J158" s="31"/>
       <c r="K158" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L158" s="33"/>
       <c r="M158" s="33"/>
@@ -17840,28 +18558,28 @@
         <v>158.0</v>
       </c>
       <c r="B159" s="14" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C159" s="14" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D159" s="27" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="E159" s="35"/>
       <c r="F159" s="29"/>
       <c r="G159" s="30" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H159" s="30" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="I159" s="30" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="J159" s="31"/>
       <c r="K159" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L159" s="33"/>
       <c r="M159" s="33"/>
@@ -17875,30 +18593,30 @@
         <v>159.0</v>
       </c>
       <c r="B160" s="14" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C160" s="14" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="D160" s="27" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="E160" s="35"/>
       <c r="F160" s="29"/>
       <c r="G160" s="30" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H160" s="30" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="I160" s="30" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="J160" s="30" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K160" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L160" s="33"/>
       <c r="M160" s="33"/>
@@ -17912,28 +18630,28 @@
         <v>160.0</v>
       </c>
       <c r="B161" s="14" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C161" s="14" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="D161" s="27" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="E161" s="35"/>
       <c r="F161" s="29"/>
       <c r="G161" s="30" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H161" s="30" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="I161" s="30" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="J161" s="31"/>
       <c r="K161" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L161" s="33"/>
       <c r="M161" s="33"/>
@@ -17947,28 +18665,28 @@
         <v>161.0</v>
       </c>
       <c r="B162" s="14" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C162" s="14" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D162" s="27" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="E162" s="35"/>
       <c r="F162" s="29"/>
       <c r="G162" s="30" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H162" s="30" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="I162" s="30" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="J162" s="31"/>
       <c r="K162" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L162" s="33"/>
       <c r="M162" s="33"/>
@@ -17982,30 +18700,30 @@
         <v>162.0</v>
       </c>
       <c r="B163" s="14" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C163" s="14" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D163" s="27" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="E163" s="35"/>
       <c r="F163" s="29"/>
       <c r="G163" s="30" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H163" s="27" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="I163" s="27" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="J163" s="30" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="K163" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L163" s="33"/>
       <c r="M163" s="33"/>
@@ -18019,30 +18737,30 @@
         <v>163.0</v>
       </c>
       <c r="B164" s="14" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C164" s="14" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D164" s="46" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="E164" s="35"/>
       <c r="F164" s="29"/>
       <c r="G164" s="30" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H164" s="30" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="I164" s="30" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="J164" s="30" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="K164" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L164" s="33"/>
       <c r="M164" s="33"/>
@@ -18056,30 +18774,30 @@
         <v>164.0</v>
       </c>
       <c r="B165" s="14" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C165" s="14" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D165" s="27" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="E165" s="35"/>
       <c r="F165" s="29"/>
       <c r="G165" s="30" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H165" s="30" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="I165" s="30" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="J165" s="30" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="K165" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L165" s="33"/>
       <c r="M165" s="33"/>
@@ -18093,30 +18811,30 @@
         <v>165.0</v>
       </c>
       <c r="B166" s="14" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C166" s="14" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="D166" s="27" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="E166" s="35"/>
       <c r="F166" s="29"/>
       <c r="G166" s="30" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H166" s="30" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="I166" s="30" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="J166" s="30" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="K166" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L166" s="33"/>
       <c r="M166" s="33"/>
@@ -18130,30 +18848,30 @@
         <v>166.0</v>
       </c>
       <c r="B167" s="14" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C167" s="14" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D167" s="27" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="E167" s="47" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="F167" s="29"/>
       <c r="G167" s="30" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H167" s="30" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="I167" s="30" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="J167" s="30"/>
       <c r="K167" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L167" s="33"/>
       <c r="M167" s="33"/>
@@ -18167,30 +18885,30 @@
         <v>167.0</v>
       </c>
       <c r="B168" s="14" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C168" s="14" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="D168" s="27" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="E168" s="47" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="F168" s="29"/>
       <c r="G168" s="30" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H168" s="30" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="I168" s="30" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="J168" s="31"/>
       <c r="K168" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L168" s="33"/>
       <c r="M168" s="33"/>
@@ -18204,28 +18922,28 @@
         <v>168.0</v>
       </c>
       <c r="B169" s="14" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C169" s="14" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D169" s="27" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="E169" s="35"/>
       <c r="F169" s="29"/>
       <c r="G169" s="30" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H169" s="30" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="I169" s="30" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="J169" s="31"/>
       <c r="K169" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L169" s="33"/>
       <c r="M169" s="33"/>
@@ -18239,28 +18957,28 @@
         <v>169.0</v>
       </c>
       <c r="B170" s="14" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C170" s="14" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D170" s="46" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="E170" s="39"/>
       <c r="F170" s="34"/>
       <c r="G170" s="48" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H170" s="48" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="I170" s="48" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="J170" s="49"/>
       <c r="K170" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L170" s="3"/>
       <c r="M170" s="3"/>
@@ -18273,28 +18991,28 @@
         <v>170.0</v>
       </c>
       <c r="B171" s="14" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C171" s="14" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D171" s="46" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="E171" s="39"/>
       <c r="F171" s="34"/>
       <c r="G171" s="48" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H171" s="48" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="I171" s="48" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="J171" s="49"/>
       <c r="K171" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L171" s="3"/>
       <c r="M171" s="3"/>
@@ -18307,28 +19025,28 @@
         <v>171.0</v>
       </c>
       <c r="B172" s="14" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C172" s="14" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="D172" s="50" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="E172" s="51"/>
       <c r="F172" s="52"/>
       <c r="G172" s="53" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H172" s="50" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="I172" s="50" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="J172" s="54"/>
       <c r="K172" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L172" s="3"/>
       <c r="M172" s="3"/>
@@ -18344,25 +19062,25 @@
         <v>26</v>
       </c>
       <c r="C173" s="14" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D173" s="27" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="E173" s="35"/>
       <c r="F173" s="29"/>
       <c r="G173" s="30" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H173" s="30" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="I173" s="30" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="J173" s="31"/>
       <c r="K173" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L173" s="33"/>
       <c r="M173" s="33"/>
@@ -18379,25 +19097,25 @@
         <v>26</v>
       </c>
       <c r="C174" s="14" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D174" s="27" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="E174" s="35"/>
       <c r="F174" s="29"/>
       <c r="G174" s="30" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H174" s="30" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="I174" s="30" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="J174" s="31"/>
       <c r="K174" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L174" s="33"/>
       <c r="M174" s="33"/>
@@ -18414,25 +19132,25 @@
         <v>26</v>
       </c>
       <c r="C175" s="14" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="D175" s="27" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="E175" s="35"/>
       <c r="F175" s="29"/>
       <c r="G175" s="30" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H175" s="30" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="I175" s="30" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="J175" s="31"/>
       <c r="K175" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L175" s="33"/>
       <c r="M175" s="33"/>
@@ -18449,27 +19167,27 @@
         <v>26</v>
       </c>
       <c r="C176" s="14" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="D176" s="27" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="E176" s="35"/>
       <c r="F176" s="29"/>
       <c r="G176" s="30" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H176" s="30" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="I176" s="30" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="J176" s="30" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="K176" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L176" s="33"/>
       <c r="M176" s="33"/>
@@ -18486,25 +19204,25 @@
         <v>26</v>
       </c>
       <c r="C177" s="14" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="D177" s="27" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="E177" s="35"/>
       <c r="F177" s="29"/>
       <c r="G177" s="30" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H177" s="30" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="I177" s="30" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="J177" s="31"/>
       <c r="K177" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L177" s="33"/>
       <c r="M177" s="33"/>
@@ -18521,27 +19239,27 @@
         <v>26</v>
       </c>
       <c r="C178" s="14" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D178" s="27" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="E178" s="35"/>
       <c r="F178" s="29"/>
       <c r="G178" s="30" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H178" s="30" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="I178" s="30" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="J178" s="30" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="K178" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L178" s="33"/>
       <c r="M178" s="33"/>
@@ -18558,25 +19276,25 @@
         <v>26</v>
       </c>
       <c r="C179" s="14" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="D179" s="50" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="E179" s="51"/>
       <c r="F179" s="52"/>
       <c r="G179" s="30" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H179" s="50" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="I179" s="50" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="J179" s="54"/>
       <c r="K179" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L179" s="33"/>
       <c r="M179" s="33"/>
@@ -18593,25 +19311,25 @@
         <v>26</v>
       </c>
       <c r="C180" s="14" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="D180" s="50" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="E180" s="35"/>
       <c r="F180" s="29"/>
       <c r="G180" s="30" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H180" s="30" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="I180" s="30" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="J180" s="31"/>
       <c r="K180" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L180" s="33"/>
       <c r="M180" s="33"/>
@@ -18628,25 +19346,25 @@
         <v>26</v>
       </c>
       <c r="C181" s="14" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="D181" s="27" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="E181" s="35"/>
       <c r="F181" s="29"/>
       <c r="G181" s="30" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H181" s="30" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="I181" s="30" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="J181" s="31"/>
       <c r="K181" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L181" s="33"/>
       <c r="M181" s="33"/>
@@ -18663,25 +19381,25 @@
         <v>26</v>
       </c>
       <c r="C182" s="14" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="D182" s="27" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="E182" s="35"/>
       <c r="F182" s="29"/>
       <c r="G182" s="30" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H182" s="30" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="I182" s="30" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="J182" s="31"/>
       <c r="K182" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L182" s="33"/>
       <c r="M182" s="33"/>
@@ -18698,25 +19416,25 @@
         <v>26</v>
       </c>
       <c r="C183" s="14" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="D183" s="27" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="E183" s="35"/>
       <c r="F183" s="29"/>
       <c r="G183" s="30" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H183" s="30" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="I183" s="30" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="J183" s="31"/>
       <c r="K183" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L183" s="33"/>
       <c r="M183" s="33"/>
@@ -18733,25 +19451,25 @@
         <v>26</v>
       </c>
       <c r="C184" s="14" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="D184" s="50" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="E184" s="51"/>
       <c r="F184" s="52"/>
       <c r="G184" s="53" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H184" s="50" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="I184" s="50" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="J184" s="31"/>
       <c r="K184" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L184" s="33"/>
       <c r="M184" s="33"/>
@@ -18765,28 +19483,28 @@
         <v>184.0</v>
       </c>
       <c r="B185" s="14" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C185" s="14" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D185" s="27" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="E185" s="35"/>
       <c r="F185" s="29"/>
       <c r="G185" s="30" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="H185" s="30" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="I185" s="30" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="J185" s="30"/>
       <c r="K185" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L185" s="33"/>
       <c r="M185" s="33"/>
@@ -18800,28 +19518,28 @@
         <v>185.0</v>
       </c>
       <c r="B186" s="14" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C186" s="14" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D186" s="27" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="E186" s="35"/>
       <c r="F186" s="29"/>
       <c r="G186" s="30" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H186" s="30" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="I186" s="30" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="J186" s="31"/>
       <c r="K186" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L186" s="33"/>
       <c r="M186" s="33"/>
@@ -18835,28 +19553,28 @@
         <v>186.0</v>
       </c>
       <c r="B187" s="14" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C187" s="14" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="D187" s="27" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="E187" s="35"/>
       <c r="F187" s="29"/>
       <c r="G187" s="30" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H187" s="30" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="I187" s="30" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="J187" s="31"/>
       <c r="K187" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L187" s="33"/>
       <c r="M187" s="33"/>
@@ -18870,30 +19588,30 @@
         <v>187.0</v>
       </c>
       <c r="B188" s="14" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C188" s="14" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="D188" s="27" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="E188" s="35"/>
       <c r="F188" s="29"/>
       <c r="G188" s="30" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H188" s="30" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="I188" s="30" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="J188" s="55" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="K188" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L188" s="33"/>
       <c r="M188" s="33"/>
@@ -18907,28 +19625,28 @@
         <v>188.0</v>
       </c>
       <c r="B189" s="14" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C189" s="14" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="D189" s="27" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="E189" s="35"/>
       <c r="F189" s="29"/>
       <c r="G189" s="30" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H189" s="30" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="I189" s="30" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="J189" s="30"/>
       <c r="K189" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L189" s="33"/>
       <c r="M189" s="33"/>
@@ -18942,28 +19660,28 @@
         <v>189.0</v>
       </c>
       <c r="B190" s="14" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C190" s="14" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D190" s="27" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="E190" s="35"/>
       <c r="F190" s="29"/>
       <c r="G190" s="30" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H190" s="30" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="I190" s="30" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="J190" s="31"/>
       <c r="K190" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L190" s="33"/>
       <c r="M190" s="33"/>
@@ -18977,30 +19695,30 @@
         <v>190.0</v>
       </c>
       <c r="B191" s="14" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C191" s="14" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D191" s="27" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="E191" s="28" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="F191" s="29"/>
       <c r="G191" s="30" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H191" s="30" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="I191" s="30" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="J191" s="31"/>
       <c r="K191" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L191" s="33"/>
       <c r="M191" s="33"/>
@@ -19014,30 +19732,30 @@
         <v>191.0</v>
       </c>
       <c r="B192" s="14" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C192" s="14" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="D192" s="27" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="E192" s="28" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="F192" s="29"/>
       <c r="G192" s="30" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H192" s="30" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="I192" s="30" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="J192" s="31"/>
       <c r="K192" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L192" s="33"/>
       <c r="M192" s="33"/>
@@ -19051,30 +19769,30 @@
         <v>192.0</v>
       </c>
       <c r="B193" s="14" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C193" s="14" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="D193" s="27" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="E193" s="28" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="F193" s="29"/>
       <c r="G193" s="30" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H193" s="30" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="I193" s="30" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="J193" s="31"/>
       <c r="K193" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L193" s="33"/>
       <c r="M193" s="33"/>
@@ -19088,28 +19806,28 @@
         <v>193.0</v>
       </c>
       <c r="B194" s="14" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C194" s="14" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="D194" s="27" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="E194" s="35"/>
       <c r="F194" s="29"/>
       <c r="G194" s="30" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H194" s="30" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="I194" s="30" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="J194" s="31"/>
       <c r="K194" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L194" s="33"/>
       <c r="M194" s="33"/>
@@ -19123,28 +19841,28 @@
         <v>194.0</v>
       </c>
       <c r="B195" s="14" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C195" s="14" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="D195" s="27" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="E195" s="35"/>
       <c r="F195" s="29"/>
       <c r="G195" s="30" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H195" s="30" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="I195" s="30" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="J195" s="31"/>
       <c r="K195" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L195" s="33"/>
       <c r="M195" s="33"/>
@@ -19158,28 +19876,28 @@
         <v>195.0</v>
       </c>
       <c r="B196" s="14" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C196" s="14" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D196" s="27" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="E196" s="35"/>
       <c r="F196" s="29"/>
       <c r="G196" s="30" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H196" s="30" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="I196" s="30" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="J196" s="31"/>
       <c r="K196" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L196" s="33"/>
       <c r="M196" s="33"/>
@@ -19196,25 +19914,25 @@
         <v>28</v>
       </c>
       <c r="C197" s="14" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="D197" s="27" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="E197" s="35"/>
       <c r="F197" s="29"/>
       <c r="G197" s="30" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H197" s="30" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="I197" s="30" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="J197" s="31"/>
       <c r="K197" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L197" s="33"/>
       <c r="M197" s="33"/>
@@ -19231,25 +19949,25 @@
         <v>28</v>
       </c>
       <c r="C198" s="14" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D198" s="27" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="E198" s="35"/>
       <c r="F198" s="29"/>
       <c r="G198" s="30" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H198" s="30" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="I198" s="30" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="J198" s="31"/>
       <c r="K198" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L198" s="33"/>
       <c r="M198" s="33"/>
@@ -19266,25 +19984,25 @@
         <v>28</v>
       </c>
       <c r="C199" s="14" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="D199" s="27" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="E199" s="35"/>
       <c r="F199" s="29"/>
       <c r="G199" s="30" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="H199" s="30" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="I199" s="30" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="J199" s="31"/>
       <c r="K199" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L199" s="33"/>
       <c r="M199" s="33"/>
@@ -19301,25 +20019,25 @@
         <v>28</v>
       </c>
       <c r="C200" s="14" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="D200" s="27" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="E200" s="35"/>
       <c r="F200" s="29"/>
       <c r="G200" s="30" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="H200" s="30" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="I200" s="30" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="J200" s="31"/>
       <c r="K200" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L200" s="33"/>
       <c r="M200" s="33"/>
@@ -19336,25 +20054,25 @@
         <v>28</v>
       </c>
       <c r="C201" s="14" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="D201" s="27" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="E201" s="35"/>
       <c r="F201" s="29"/>
       <c r="G201" s="30" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="H201" s="30" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="I201" s="30" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="J201" s="31"/>
       <c r="K201" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L201" s="33"/>
       <c r="M201" s="33"/>
@@ -19371,25 +20089,25 @@
         <v>28</v>
       </c>
       <c r="C202" s="14" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="D202" s="27" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="E202" s="35"/>
       <c r="F202" s="29"/>
       <c r="G202" s="30" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="H202" s="30" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="I202" s="30" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="J202" s="31"/>
       <c r="K202" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L202" s="33"/>
       <c r="M202" s="33"/>
@@ -19406,25 +20124,25 @@
         <v>28</v>
       </c>
       <c r="C203" s="14" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="D203" s="27" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="E203" s="35"/>
       <c r="F203" s="29"/>
       <c r="G203" s="30" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H203" s="30" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="I203" s="30" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="J203" s="31"/>
       <c r="K203" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L203" s="33"/>
       <c r="M203" s="33"/>
@@ -19441,25 +20159,25 @@
         <v>28</v>
       </c>
       <c r="C204" s="14" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="D204" s="27" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="E204" s="35"/>
       <c r="F204" s="29"/>
       <c r="G204" s="30" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H204" s="30" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="I204" s="30" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="J204" s="31"/>
       <c r="K204" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L204" s="33"/>
       <c r="M204" s="33"/>
@@ -19476,25 +20194,25 @@
         <v>28</v>
       </c>
       <c r="C205" s="14" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="D205" s="27" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="E205" s="35"/>
       <c r="F205" s="29"/>
       <c r="G205" s="30" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H205" s="30" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="I205" s="30" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="J205" s="31"/>
       <c r="K205" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L205" s="33"/>
       <c r="M205" s="33"/>
@@ -19511,25 +20229,25 @@
         <v>28</v>
       </c>
       <c r="C206" s="14" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="D206" s="27" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="E206" s="35"/>
       <c r="F206" s="29"/>
       <c r="G206" s="30" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H206" s="30" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="I206" s="30" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="J206" s="31"/>
       <c r="K206" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L206" s="33"/>
       <c r="M206" s="33"/>
@@ -19546,25 +20264,25 @@
         <v>29</v>
       </c>
       <c r="C207" s="14" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="D207" s="27" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="E207" s="35"/>
       <c r="F207" s="29"/>
       <c r="G207" s="30" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="H207" s="30" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="I207" s="30" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="J207" s="31"/>
       <c r="K207" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L207" s="33"/>
       <c r="M207" s="33"/>
@@ -19581,25 +20299,25 @@
         <v>29</v>
       </c>
       <c r="C208" s="14" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="D208" s="27" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="E208" s="35"/>
       <c r="F208" s="29"/>
       <c r="G208" s="30" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="H208" s="30" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="I208" s="30" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="J208" s="31"/>
       <c r="K208" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L208" s="33"/>
       <c r="M208" s="33"/>
@@ -19616,25 +20334,25 @@
         <v>29</v>
       </c>
       <c r="C209" s="14" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="D209" s="27" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="E209" s="35"/>
       <c r="F209" s="29"/>
       <c r="G209" s="30" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H209" s="30" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="I209" s="30" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="J209" s="31"/>
       <c r="K209" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L209" s="33"/>
       <c r="M209" s="33"/>
@@ -19651,25 +20369,25 @@
         <v>29</v>
       </c>
       <c r="C210" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="D210" s="27" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E210" s="35"/>
       <c r="F210" s="29"/>
       <c r="G210" s="30" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H210" s="30" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="I210" s="30" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="J210" s="31"/>
       <c r="K210" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L210" s="33"/>
       <c r="M210" s="33"/>
@@ -19686,25 +20404,25 @@
         <v>29</v>
       </c>
       <c r="C211" s="14" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="D211" s="27" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="E211" s="35"/>
       <c r="F211" s="29"/>
       <c r="G211" s="30" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H211" s="30" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="I211" s="30" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="J211" s="31"/>
       <c r="K211" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L211" s="33"/>
       <c r="M211" s="33"/>
@@ -19721,25 +20439,25 @@
         <v>29</v>
       </c>
       <c r="C212" s="14" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="D212" s="27" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="E212" s="35"/>
       <c r="F212" s="29"/>
       <c r="G212" s="30" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H212" s="30" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="I212" s="30" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="J212" s="31"/>
       <c r="K212" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L212" s="33"/>
       <c r="M212" s="33"/>
@@ -19756,25 +20474,25 @@
         <v>29</v>
       </c>
       <c r="C213" s="14" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="D213" s="27" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="E213" s="35"/>
       <c r="F213" s="29"/>
       <c r="G213" s="30" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H213" s="30" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="I213" s="30" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="J213" s="31"/>
       <c r="K213" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L213" s="33"/>
       <c r="M213" s="33"/>
@@ -19791,25 +20509,25 @@
         <v>29</v>
       </c>
       <c r="C214" s="14" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="D214" s="27" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="E214" s="35"/>
       <c r="F214" s="29"/>
       <c r="G214" s="30" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H214" s="30" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="I214" s="30" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="J214" s="31"/>
       <c r="K214" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L214" s="33"/>
       <c r="M214" s="33"/>
@@ -19826,25 +20544,25 @@
         <v>29</v>
       </c>
       <c r="C215" s="14" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="D215" s="27" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="E215" s="35"/>
       <c r="F215" s="29"/>
       <c r="G215" s="30" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H215" s="30" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="I215" s="30" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="J215" s="31"/>
       <c r="K215" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L215" s="33"/>
       <c r="M215" s="33"/>
@@ -34167,55 +34885,55 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="58" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" s="59" t="s">
         <v>9</v>
       </c>
       <c r="C1" s="59" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D1" s="60" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E1" s="60" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F1" s="60" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G1" s="60" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H1" s="60" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I1" s="60" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J1" s="60" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K1" s="23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L1" s="23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M1" s="23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N1" s="23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O1" s="23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P1" s="23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q1" s="61" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R1" s="25"/>
       <c r="S1" s="25"/>
@@ -34235,27 +34953,27 @@
         <v>31</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="F2" s="62"/>
       <c r="G2" s="44" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="H2" s="44" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="I2" s="44" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="J2" s="29"/>
       <c r="K2" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L2" s="33"/>
       <c r="M2" s="33"/>
@@ -34272,27 +34990,27 @@
         <v>31</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="E3" s="27" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="F3" s="62"/>
       <c r="G3" s="44" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H3" s="44" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="I3" s="44" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="J3" s="29"/>
       <c r="K3" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L3" s="33"/>
       <c r="M3" s="33"/>
@@ -34309,27 +35027,27 @@
         <v>31</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="F4" s="62"/>
       <c r="G4" s="44" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H4" s="44" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="I4" s="44" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="J4" s="29"/>
       <c r="K4" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L4" s="33"/>
       <c r="M4" s="33"/>
@@ -34346,25 +35064,25 @@
         <v>31</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="E5" s="40"/>
       <c r="F5" s="62"/>
       <c r="G5" s="44" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="H5" s="44" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="I5" s="44" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="J5" s="29"/>
       <c r="K5" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L5" s="33"/>
       <c r="M5" s="33"/>
@@ -34381,27 +35099,27 @@
         <v>31</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="E6" s="27" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="F6" s="62"/>
       <c r="G6" s="44" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H6" s="44" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="I6" s="44" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="J6" s="29"/>
       <c r="K6" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L6" s="33"/>
       <c r="M6" s="33"/>
@@ -34418,27 +35136,27 @@
         <v>31</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="F7" s="62"/>
       <c r="G7" s="44" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H7" s="44" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="I7" s="44" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="J7" s="29"/>
       <c r="K7" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L7" s="33"/>
       <c r="M7" s="33"/>
@@ -34455,27 +35173,27 @@
         <v>31</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="F8" s="62"/>
       <c r="G8" s="44" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="H8" s="44" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="I8" s="44" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="J8" s="29"/>
       <c r="K8" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L8" s="33"/>
       <c r="M8" s="33"/>
@@ -34492,27 +35210,27 @@
         <v>31</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="F9" s="62"/>
       <c r="G9" s="44" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H9" s="44" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="I9" s="44" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="J9" s="29"/>
       <c r="K9" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L9" s="33"/>
       <c r="M9" s="33"/>
@@ -34529,25 +35247,25 @@
         <v>31</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="E10" s="40"/>
       <c r="F10" s="62"/>
       <c r="G10" s="44" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H10" s="44" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="I10" s="44" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="J10" s="29"/>
       <c r="K10" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L10" s="33"/>
       <c r="M10" s="33"/>
@@ -34564,25 +35282,25 @@
         <v>32</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="E11" s="40"/>
       <c r="F11" s="62"/>
       <c r="G11" s="44" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="H11" s="44" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="I11" s="44" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="J11" s="29"/>
       <c r="K11" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L11" s="33"/>
       <c r="M11" s="33"/>
@@ -34599,27 +35317,27 @@
         <v>32</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="F12" s="62"/>
       <c r="G12" s="44" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="H12" s="44" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="I12" s="44" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="J12" s="29"/>
       <c r="K12" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L12" s="33"/>
       <c r="M12" s="33"/>
@@ -34636,27 +35354,27 @@
         <v>32</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="F13" s="62"/>
       <c r="G13" s="44" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="H13" s="44" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="I13" s="44" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="J13" s="29"/>
       <c r="K13" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L13" s="33"/>
       <c r="M13" s="33"/>
@@ -34673,23 +35391,23 @@
         <v>32</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="E14" s="27"/>
       <c r="F14" s="62"/>
       <c r="G14" s="44" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="H14" s="44" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="I14" s="37"/>
       <c r="J14" s="29"/>
       <c r="K14" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L14" s="33"/>
       <c r="M14" s="33"/>
@@ -34706,25 +35424,25 @@
         <v>32</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="F15" s="62"/>
       <c r="G15" s="44" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="H15" s="44" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="I15" s="37"/>
       <c r="J15" s="29"/>
       <c r="K15" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L15" s="33"/>
       <c r="M15" s="33"/>
@@ -34741,25 +35459,25 @@
         <v>32</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="F16" s="62"/>
       <c r="G16" s="44" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="H16" s="44" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="I16" s="37"/>
       <c r="J16" s="29"/>
       <c r="K16" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L16" s="33"/>
       <c r="M16" s="33"/>
@@ -34769,148 +35487,290 @@
       <c r="Q16" s="36"/>
     </row>
     <row r="17">
-      <c r="A17" s="3"/>
-      <c r="B17" s="56"/>
-      <c r="C17" s="56"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="63"/>
-      <c r="G17" s="64"/>
-      <c r="H17" s="64"/>
-      <c r="I17" s="64"/>
-      <c r="J17" s="34"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
+      <c r="A17" s="14">
+        <v>16.0</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>1074</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>1075</v>
+      </c>
+      <c r="F17" s="62"/>
+      <c r="G17" s="44" t="s">
+        <v>1076</v>
+      </c>
+      <c r="H17" s="44" t="s">
+        <v>1077</v>
+      </c>
+      <c r="I17" s="44" t="s">
+        <v>1077</v>
+      </c>
+      <c r="J17" s="29"/>
+      <c r="K17" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="L17" s="33"/>
+      <c r="M17" s="33"/>
+      <c r="N17" s="33"/>
+      <c r="O17" s="33"/>
+      <c r="P17" s="33"/>
+      <c r="Q17" s="36"/>
     </row>
     <row r="18">
-      <c r="A18" s="3"/>
-      <c r="B18" s="56"/>
-      <c r="C18" s="56"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="57"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="64"/>
-      <c r="H18" s="64"/>
-      <c r="I18" s="64"/>
-      <c r="J18" s="34"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
+      <c r="A18" s="14">
+        <v>17.0</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D18" s="27" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E18" s="27" t="s">
+        <v>1080</v>
+      </c>
+      <c r="F18" s="62"/>
+      <c r="G18" s="44" t="s">
+        <v>1081</v>
+      </c>
+      <c r="H18" s="44" t="s">
+        <v>1082</v>
+      </c>
+      <c r="I18" s="44" t="s">
+        <v>1083</v>
+      </c>
+      <c r="J18" s="29"/>
+      <c r="K18" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="L18" s="33"/>
+      <c r="M18" s="33"/>
+      <c r="N18" s="33"/>
+      <c r="O18" s="33"/>
+      <c r="P18" s="33"/>
+      <c r="Q18" s="36"/>
     </row>
     <row r="19">
-      <c r="A19" s="3"/>
-      <c r="B19" s="56"/>
-      <c r="C19" s="56"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="63"/>
-      <c r="G19" s="64"/>
-      <c r="H19" s="64"/>
-      <c r="I19" s="64"/>
-      <c r="J19" s="34"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
+      <c r="A19" s="14">
+        <v>18.0</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E19" s="40"/>
+      <c r="F19" s="62"/>
+      <c r="G19" s="44" t="s">
+        <v>1086</v>
+      </c>
+      <c r="H19" s="44" t="s">
+        <v>1087</v>
+      </c>
+      <c r="I19" s="44" t="s">
+        <v>1087</v>
+      </c>
+      <c r="J19" s="29"/>
+      <c r="K19" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="L19" s="33"/>
+      <c r="M19" s="33"/>
+      <c r="N19" s="33"/>
+      <c r="O19" s="33"/>
+      <c r="P19" s="33"/>
+      <c r="Q19" s="36"/>
     </row>
     <row r="20">
-      <c r="A20" s="3"/>
-      <c r="B20" s="56"/>
-      <c r="C20" s="56"/>
-      <c r="D20" s="57"/>
-      <c r="E20" s="57"/>
-      <c r="F20" s="63"/>
-      <c r="G20" s="64"/>
-      <c r="H20" s="64"/>
-      <c r="I20" s="64"/>
-      <c r="J20" s="34"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
-      <c r="P20" s="3"/>
+      <c r="A20" s="14">
+        <v>19.0</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D20" s="27" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E20" s="40"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="44" t="s">
+        <v>1090</v>
+      </c>
+      <c r="H20" s="44" t="s">
+        <v>1091</v>
+      </c>
+      <c r="I20" s="44" t="s">
+        <v>1091</v>
+      </c>
+      <c r="J20" s="29"/>
+      <c r="K20" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="L20" s="33"/>
+      <c r="M20" s="33"/>
+      <c r="N20" s="33"/>
+      <c r="O20" s="33"/>
+      <c r="P20" s="33"/>
+      <c r="Q20" s="36"/>
     </row>
     <row r="21">
-      <c r="A21" s="3"/>
-      <c r="B21" s="56"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="57"/>
-      <c r="E21" s="57"/>
-      <c r="F21" s="63"/>
-      <c r="G21" s="64"/>
-      <c r="H21" s="64"/>
-      <c r="I21" s="64"/>
-      <c r="J21" s="34"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
-      <c r="P21" s="3"/>
+      <c r="A21" s="14">
+        <v>20.0</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D21" s="27" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E21" s="40"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="44" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H21" s="44" t="s">
+        <v>1095</v>
+      </c>
+      <c r="I21" s="44" t="s">
+        <v>1095</v>
+      </c>
+      <c r="J21" s="29"/>
+      <c r="K21" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="L21" s="33"/>
+      <c r="M21" s="33"/>
+      <c r="N21" s="33"/>
+      <c r="O21" s="33"/>
+      <c r="P21" s="33"/>
+      <c r="Q21" s="36"/>
     </row>
     <row r="22">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="57"/>
-      <c r="E22" s="57"/>
-      <c r="F22" s="63"/>
-      <c r="G22" s="64"/>
-      <c r="H22" s="64"/>
-      <c r="I22" s="64"/>
-      <c r="J22" s="34"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="3"/>
-      <c r="P22" s="3"/>
+      <c r="A22" s="14">
+        <v>21.0</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D22" s="27" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E22" s="40"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="44" t="s">
+        <v>1098</v>
+      </c>
+      <c r="H22" s="44" t="s">
+        <v>1099</v>
+      </c>
+      <c r="I22" s="44" t="s">
+        <v>1099</v>
+      </c>
+      <c r="J22" s="29"/>
+      <c r="K22" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="L22" s="33"/>
+      <c r="M22" s="33"/>
+      <c r="N22" s="33"/>
+      <c r="O22" s="33"/>
+      <c r="P22" s="33"/>
+      <c r="Q22" s="36"/>
     </row>
     <row r="23">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="57"/>
-      <c r="E23" s="57"/>
-      <c r="F23" s="63"/>
-      <c r="G23" s="64"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="64"/>
-      <c r="J23" s="34"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="3"/>
-      <c r="P23" s="3"/>
+      <c r="A23" s="14">
+        <v>22.0</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D23" s="27" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E23" s="40"/>
+      <c r="F23" s="62"/>
+      <c r="G23" s="44" t="s">
+        <v>1102</v>
+      </c>
+      <c r="H23" s="44" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I23" s="44" t="s">
+        <v>1103</v>
+      </c>
+      <c r="J23" s="29"/>
+      <c r="K23" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="L23" s="33"/>
+      <c r="M23" s="33"/>
+      <c r="N23" s="33"/>
+      <c r="O23" s="33"/>
+      <c r="P23" s="33"/>
+      <c r="Q23" s="36"/>
     </row>
     <row r="24">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="57"/>
-      <c r="E24" s="57"/>
-      <c r="F24" s="63"/>
-      <c r="G24" s="64"/>
-      <c r="H24" s="64"/>
-      <c r="I24" s="64"/>
-      <c r="J24" s="34"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
+      <c r="A24" s="14">
+        <v>23.0</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D24" s="27" t="s">
+        <v>1105</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>1106</v>
+      </c>
+      <c r="F24" s="62"/>
+      <c r="G24" s="44" t="s">
+        <v>1107</v>
+      </c>
+      <c r="H24" s="44" t="s">
+        <v>1108</v>
+      </c>
+      <c r="I24" s="44" t="s">
+        <v>1109</v>
+      </c>
+      <c r="J24" s="29"/>
+      <c r="K24" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="L24" s="33"/>
+      <c r="M24" s="33"/>
+      <c r="N24" s="33"/>
+      <c r="O24" s="33"/>
+      <c r="P24" s="33"/>
+      <c r="Q24" s="36"/>
     </row>
     <row r="25">
       <c r="A25" s="3"/>
